--- a/dist/产品库存及周转统计.xlsx
+++ b/dist/产品库存及周转统计.xlsx
@@ -4,20 +4,20 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="32320" windowHeight="16160"/>
+    <workbookView windowHeight="16160"/>
   </bookViews>
   <sheets>
     <sheet name="产品库存" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">产品库存!$A$1:$AH$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">产品库存!$A$1:$AH$54</definedName>
   </definedNames>
   <calcPr calcId="144525" concurrentCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="268">
   <si>
     <t>名称</t>
   </si>
@@ -763,6 +763,78 @@
   </si>
   <si>
     <t>X00334LMMB</t>
+  </si>
+  <si>
+    <t>新床边双钩（灰）1p</t>
+  </si>
+  <si>
+    <t>B0GS6WPD9F</t>
+  </si>
+  <si>
+    <t>bedsidecaddy_2bag_gray_1pcs</t>
+  </si>
+  <si>
+    <t>X005163XD5</t>
+  </si>
+  <si>
+    <t>新床边双钩（灰）2p</t>
+  </si>
+  <si>
+    <t>B0GS6Y7LDG</t>
+  </si>
+  <si>
+    <t>bedsidecaddy_2bag_gray_2pcs</t>
+  </si>
+  <si>
+    <t>X00515YR59</t>
+  </si>
+  <si>
+    <t>新床边双钩（粉）1p</t>
+  </si>
+  <si>
+    <t>B0GS71NZ7Q</t>
+  </si>
+  <si>
+    <t>bedsidecaddy_2bag_pink_1pcs</t>
+  </si>
+  <si>
+    <t>X005165LUD</t>
+  </si>
+  <si>
+    <t>新床边双钩（粉）2p</t>
+  </si>
+  <si>
+    <t>B0GS6YFWT7</t>
+  </si>
+  <si>
+    <t>bedsidecaddy_2bag_pink_2pc</t>
+  </si>
+  <si>
+    <t>X005160JTB</t>
+  </si>
+  <si>
+    <t>新床边双钩（白）1p</t>
+  </si>
+  <si>
+    <t>B0GS6WZJJG</t>
+  </si>
+  <si>
+    <t>bedsidecaddy_2bag_white_1pcs</t>
+  </si>
+  <si>
+    <t>X005160HRZ</t>
+  </si>
+  <si>
+    <t>新床边双钩（白）2p</t>
+  </si>
+  <si>
+    <t>B0GS76LHWM</t>
+  </si>
+  <si>
+    <t>bedsidecaddy_2bag_white_2pc</t>
+  </si>
+  <si>
+    <t>X005166XCN</t>
   </si>
 </sst>
 </file>
@@ -1490,7 +1562,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1562,6 +1634,9 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2005,16 +2080,16 @@
       <c r="E1" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="24" t="s">
+      <c r="F1" s="25" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="25" t="s">
+      <c r="H1" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="32" t="s">
+      <c r="I1" s="33" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="8" t="s">
@@ -2030,34 +2105,34 @@
       <c r="N1" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="33" t="s">
+      <c r="O1" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="Q1" s="34" t="s">
+      <c r="Q1" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="R1" s="34" t="s">
+      <c r="R1" s="35" t="s">
         <v>15</v>
       </c>
       <c r="T1" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="U1" s="35" t="s">
+      <c r="U1" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="V1" s="35" t="s">
+      <c r="V1" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="W1" s="35" t="s">
+      <c r="W1" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="X1" s="35" t="s">
+      <c r="X1" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="Y1" s="35" t="s">
+      <c r="Y1" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="Z1" s="35" t="s">
+      <c r="Z1" s="36" t="s">
         <v>22</v>
       </c>
       <c r="AD1" s="7" t="s">
@@ -2089,29 +2164,29 @@
       <c r="D2" s="9">
         <v>0</v>
       </c>
-      <c r="E2" s="26">
-        <f t="shared" ref="E2:E53" si="0">C2+D2</f>
-        <v>0</v>
-      </c>
-      <c r="F2" s="27">
+      <c r="E2" s="27">
+        <f t="shared" ref="E2:E60" si="0">C2+D2</f>
+        <v>0</v>
+      </c>
+      <c r="F2" s="28">
         <v>16.4</v>
       </c>
-      <c r="G2" s="28">
+      <c r="G2" s="29">
         <v>13.8</v>
       </c>
-      <c r="H2" s="25">
+      <c r="H2" s="26">
         <v>20.5</v>
       </c>
-      <c r="I2" s="25">
+      <c r="I2" s="26">
         <f t="shared" ref="I2:I19" si="1">MAX(F2,G2)*1.375</f>
         <v>22.55</v>
       </c>
-      <c r="J2" s="25">
-        <f t="shared" ref="J2:J53" si="2">(C2)/I2</f>
-        <v>0</v>
-      </c>
-      <c r="K2" s="25">
-        <f t="shared" ref="K2:K53" si="3">(E2)/I2</f>
+      <c r="J2" s="26">
+        <f t="shared" ref="J2:J60" si="2">(C2)/I2</f>
+        <v>0</v>
+      </c>
+      <c r="K2" s="26">
+        <f t="shared" ref="K2:K60" si="3">(E2)/I2</f>
         <v>0</v>
       </c>
       <c r="L2" s="17"/>
@@ -2121,30 +2196,30 @@
       <c r="N2" s="17">
         <v>6</v>
       </c>
-      <c r="O2" s="33">
+      <c r="O2" s="34">
         <f t="shared" ref="O2:O45" si="4">M2+N2</f>
         <v>25.43</v>
       </c>
-      <c r="Q2" s="34">
+      <c r="Q2" s="35">
         <f t="shared" ref="Q2:Q45" si="5">M2*C2</f>
         <v>0</v>
       </c>
-      <c r="R2" s="34">
+      <c r="R2" s="35">
         <f t="shared" ref="R2:R45" si="6">M2*D2</f>
         <v>0</v>
       </c>
       <c r="T2" s="7">
         <v>36</v>
       </c>
-      <c r="U2" s="36"/>
-      <c r="V2" s="36"/>
-      <c r="W2" s="37">
+      <c r="U2" s="37"/>
+      <c r="V2" s="37"/>
+      <c r="W2" s="38">
         <f>CEILING(MAX(0,135-MAX(K2,60))*I2/T2,1)*T2</f>
         <v>1692</v>
       </c>
-      <c r="X2" s="36"/>
-      <c r="Y2" s="36"/>
-      <c r="Z2" s="37">
+      <c r="X2" s="37"/>
+      <c r="Y2" s="37"/>
+      <c r="Z2" s="38">
         <f>MIN(CEILING(MAX(0,115-MAX(J2,30))*I2/T2,1)*T2,D2)</f>
         <v>0</v>
       </c>
@@ -2177,28 +2252,28 @@
       <c r="D3" s="9">
         <v>0</v>
       </c>
-      <c r="E3" s="26">
+      <c r="E3" s="27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F3" s="27">
+      <c r="F3" s="28">
         <v>5.7</v>
       </c>
-      <c r="G3" s="28">
+      <c r="G3" s="29">
         <v>5.3</v>
       </c>
-      <c r="H3" s="25">
+      <c r="H3" s="26">
         <v>8</v>
       </c>
-      <c r="I3" s="25">
+      <c r="I3" s="26">
         <f t="shared" si="1"/>
         <v>7.8375</v>
       </c>
-      <c r="J3" s="25">
+      <c r="J3" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K3" s="25">
+      <c r="K3" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -2209,30 +2284,30 @@
       <c r="N3" s="17">
         <v>10</v>
       </c>
-      <c r="O3" s="33">
+      <c r="O3" s="34">
         <f t="shared" si="4"/>
         <v>34.37</v>
       </c>
-      <c r="Q3" s="34">
+      <c r="Q3" s="35">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="R3" s="34">
+      <c r="R3" s="35">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T3" s="7">
         <v>32</v>
       </c>
-      <c r="U3" s="36"/>
-      <c r="V3" s="36"/>
-      <c r="W3" s="37">
+      <c r="U3" s="37"/>
+      <c r="V3" s="37"/>
+      <c r="W3" s="38">
         <f>CEILING(MAX(0,135-MAX(K3,60))*I3/T3,1)*T3</f>
         <v>608</v>
       </c>
-      <c r="X3" s="36"/>
-      <c r="Y3" s="36"/>
-      <c r="Z3" s="37">
+      <c r="X3" s="37"/>
+      <c r="Y3" s="37"/>
+      <c r="Z3" s="38">
         <f>MIN(CEILING(MAX(0,115-MAX(J3,30))*I3/T3,1)*T3,D3)</f>
         <v>0</v>
       </c>
@@ -2265,28 +2340,28 @@
       <c r="D4" s="9">
         <v>0</v>
       </c>
-      <c r="E4" s="26">
+      <c r="E4" s="27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F4" s="27">
+      <c r="F4" s="28">
         <v>5.4</v>
       </c>
-      <c r="G4" s="28">
+      <c r="G4" s="29">
         <v>6.1</v>
       </c>
-      <c r="H4" s="25">
+      <c r="H4" s="26">
         <v>8</v>
       </c>
-      <c r="I4" s="25">
+      <c r="I4" s="26">
         <f t="shared" si="1"/>
         <v>8.3875</v>
       </c>
-      <c r="J4" s="25">
+      <c r="J4" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K4" s="25">
+      <c r="K4" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -2297,30 +2372,30 @@
       <c r="N4" s="17">
         <v>6.98</v>
       </c>
-      <c r="O4" s="33">
+      <c r="O4" s="34">
         <f t="shared" si="4"/>
         <v>29.72</v>
       </c>
-      <c r="Q4" s="34">
+      <c r="Q4" s="35">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="R4" s="34">
+      <c r="R4" s="35">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T4" s="7">
         <v>42</v>
       </c>
-      <c r="U4" s="36"/>
-      <c r="V4" s="36"/>
-      <c r="W4" s="37">
+      <c r="U4" s="37"/>
+      <c r="V4" s="37"/>
+      <c r="W4" s="38">
         <f>CEILING(MAX(0,135-MAX(K4,60))*I4/T4,1)*T4</f>
         <v>630</v>
       </c>
-      <c r="X4" s="36"/>
-      <c r="Y4" s="36"/>
-      <c r="Z4" s="37">
+      <c r="X4" s="37"/>
+      <c r="Y4" s="37"/>
+      <c r="Z4" s="38">
         <f>MIN(CEILING(MAX(0,115-MAX(J4,30))*I4/T4,1)*T4,D4)</f>
         <v>0</v>
       </c>
@@ -2353,28 +2428,28 @@
       <c r="D5" s="9">
         <v>0</v>
       </c>
-      <c r="E5" s="26">
+      <c r="E5" s="27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F5" s="27">
+      <c r="F5" s="28">
         <v>10</v>
       </c>
-      <c r="G5" s="28">
+      <c r="G5" s="29">
         <v>11.5</v>
       </c>
-      <c r="H5" s="25">
+      <c r="H5" s="26">
         <v>17</v>
       </c>
-      <c r="I5" s="25">
+      <c r="I5" s="26">
         <f t="shared" si="1"/>
         <v>15.8125</v>
       </c>
-      <c r="J5" s="25">
+      <c r="J5" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K5" s="25">
+      <c r="K5" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -2385,30 +2460,30 @@
       <c r="N5" s="17">
         <v>10</v>
       </c>
-      <c r="O5" s="33">
+      <c r="O5" s="34">
         <f t="shared" si="4"/>
         <v>34.37</v>
       </c>
-      <c r="Q5" s="34">
+      <c r="Q5" s="35">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="R5" s="34">
+      <c r="R5" s="35">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T5" s="7">
         <v>32</v>
       </c>
-      <c r="U5" s="36"/>
-      <c r="V5" s="36"/>
-      <c r="W5" s="37">
+      <c r="U5" s="37"/>
+      <c r="V5" s="37"/>
+      <c r="W5" s="38">
         <f>CEILING(MAX(0,135-MAX(K5,60))*I5/T5,1)*T5</f>
         <v>1216</v>
       </c>
-      <c r="X5" s="36"/>
-      <c r="Y5" s="36"/>
-      <c r="Z5" s="37">
+      <c r="X5" s="37"/>
+      <c r="Y5" s="37"/>
+      <c r="Z5" s="38">
         <f>MIN(CEILING(MAX(0,115-MAX(J5,30))*I5/T5,1)*T5,D5)</f>
         <v>0</v>
       </c>
@@ -2441,28 +2516,28 @@
       <c r="D6" s="9">
         <v>0</v>
       </c>
-      <c r="E6" s="26">
+      <c r="E6" s="27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F6" s="27">
+      <c r="F6" s="28">
         <v>9.2</v>
       </c>
-      <c r="G6" s="28">
+      <c r="G6" s="29">
         <v>9.4</v>
       </c>
-      <c r="H6" s="25">
+      <c r="H6" s="26">
         <v>13.5</v>
       </c>
-      <c r="I6" s="25">
+      <c r="I6" s="26">
         <f t="shared" si="1"/>
         <v>12.925</v>
       </c>
-      <c r="J6" s="25">
+      <c r="J6" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K6" s="25">
+      <c r="K6" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -2473,30 +2548,30 @@
       <c r="N6" s="17">
         <v>10</v>
       </c>
-      <c r="O6" s="33">
+      <c r="O6" s="34">
         <f t="shared" si="4"/>
         <v>36.57</v>
       </c>
-      <c r="Q6" s="34">
+      <c r="Q6" s="35">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="R6" s="34">
+      <c r="R6" s="35">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T6" s="7">
         <v>32</v>
       </c>
-      <c r="U6" s="36"/>
-      <c r="V6" s="36"/>
-      <c r="W6" s="37">
+      <c r="U6" s="37"/>
+      <c r="V6" s="37"/>
+      <c r="W6" s="38">
         <f>CEILING(MAX(0,135-MAX(K6,60))*I6/T6,1)*T6</f>
         <v>992</v>
       </c>
-      <c r="X6" s="36"/>
-      <c r="Y6" s="36"/>
-      <c r="Z6" s="37">
+      <c r="X6" s="37"/>
+      <c r="Y6" s="37"/>
+      <c r="Z6" s="38">
         <f>MIN(CEILING(MAX(0,115-MAX(J6,30))*I6/T6,1)*T6,D6)</f>
         <v>0</v>
       </c>
@@ -2529,28 +2604,28 @@
       <c r="D7" s="9">
         <v>0</v>
       </c>
-      <c r="E7" s="26">
+      <c r="E7" s="27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F7" s="27">
+      <c r="F7" s="28">
         <v>1</v>
       </c>
-      <c r="G7" s="28">
+      <c r="G7" s="29">
         <v>1.3</v>
       </c>
-      <c r="H7" s="25">
+      <c r="H7" s="26">
         <v>2.5</v>
       </c>
-      <c r="I7" s="25">
+      <c r="I7" s="26">
         <f t="shared" si="1"/>
         <v>1.7875</v>
       </c>
-      <c r="J7" s="25">
+      <c r="J7" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K7" s="25">
+      <c r="K7" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -2561,33 +2636,33 @@
       <c r="N7" s="17">
         <v>13.38</v>
       </c>
-      <c r="O7" s="33">
+      <c r="O7" s="34">
         <f t="shared" si="4"/>
         <v>49.49</v>
       </c>
-      <c r="Q7" s="34">
+      <c r="Q7" s="35">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="R7" s="34">
+      <c r="R7" s="35">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T7" s="7">
         <v>12</v>
       </c>
-      <c r="U7" s="36"/>
-      <c r="V7" s="37">
+      <c r="U7" s="37"/>
+      <c r="V7" s="38">
         <f>CEILING(MAX(0,120-MAX(K7,60))*I7/T7,1)*T7</f>
         <v>108</v>
       </c>
-      <c r="W7" s="36"/>
-      <c r="X7" s="36"/>
-      <c r="Y7" s="37">
+      <c r="W7" s="37"/>
+      <c r="X7" s="37"/>
+      <c r="Y7" s="38">
         <f>MIN(CEILING(MAX(0,100-MAX(J7,30))*I7/T7,1)*T7,D7)</f>
         <v>0</v>
       </c>
-      <c r="Z7" s="36"/>
+      <c r="Z7" s="37"/>
       <c r="AD7" s="7" t="s">
         <v>50</v>
       </c>
@@ -2617,29 +2692,29 @@
       <c r="D8" s="9">
         <v>0</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F8" s="27">
+      <c r="F8" s="28">
         <v>1.7</v>
       </c>
-      <c r="G8" s="28">
+      <c r="G8" s="29">
         <v>1.6</v>
       </c>
-      <c r="H8" s="25">
+      <c r="H8" s="26">
         <f t="shared" ref="H8:H14" si="7">MAX(E8,F8)*1.375</f>
         <v>2.3375</v>
       </c>
-      <c r="I8" s="25">
+      <c r="I8" s="26">
         <f t="shared" si="1"/>
         <v>2.3375</v>
       </c>
-      <c r="J8" s="25">
+      <c r="J8" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K8" s="25">
+      <c r="K8" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -2650,33 +2725,33 @@
       <c r="N8" s="17">
         <v>10.47</v>
       </c>
-      <c r="O8" s="33">
+      <c r="O8" s="34">
         <f t="shared" si="4"/>
         <v>44.18</v>
       </c>
-      <c r="Q8" s="34">
+      <c r="Q8" s="35">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="R8" s="34">
+      <c r="R8" s="35">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T8" s="7">
         <v>15</v>
       </c>
-      <c r="U8" s="36"/>
-      <c r="V8" s="37">
+      <c r="U8" s="37"/>
+      <c r="V8" s="38">
         <f t="shared" ref="V8:V15" si="8">CEILING(MAX(0,120-MAX(K8,60))*I8/T8,1)*T8</f>
         <v>150</v>
       </c>
-      <c r="W8" s="36"/>
-      <c r="X8" s="36"/>
-      <c r="Y8" s="37">
+      <c r="W8" s="37"/>
+      <c r="X8" s="37"/>
+      <c r="Y8" s="38">
         <f t="shared" ref="Y8:Y15" si="9">MIN(CEILING(MAX(0,100-MAX(J8,30))*I8/T8,1)*T8,D8)</f>
         <v>0</v>
       </c>
-      <c r="Z8" s="36"/>
+      <c r="Z8" s="37"/>
       <c r="AD8" s="7" t="s">
         <v>54</v>
       </c>
@@ -2706,28 +2781,28 @@
       <c r="D9" s="9">
         <v>0</v>
       </c>
-      <c r="E9" s="26">
+      <c r="E9" s="27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F9" s="27">
+      <c r="F9" s="28">
         <v>1.7</v>
       </c>
-      <c r="G9" s="28">
+      <c r="G9" s="29">
         <v>1.3</v>
       </c>
-      <c r="H9" s="25">
+      <c r="H9" s="26">
         <v>5</v>
       </c>
-      <c r="I9" s="25">
+      <c r="I9" s="26">
         <f t="shared" si="1"/>
         <v>2.3375</v>
       </c>
-      <c r="J9" s="25">
+      <c r="J9" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K9" s="25">
+      <c r="K9" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -2738,33 +2813,33 @@
       <c r="N9" s="17">
         <v>9</v>
       </c>
-      <c r="O9" s="33">
+      <c r="O9" s="34">
         <f t="shared" si="4"/>
         <v>37.52</v>
       </c>
-      <c r="Q9" s="34">
+      <c r="Q9" s="35">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="R9" s="34">
+      <c r="R9" s="35">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T9" s="7">
         <v>28</v>
       </c>
-      <c r="U9" s="36"/>
-      <c r="V9" s="37">
+      <c r="U9" s="37"/>
+      <c r="V9" s="38">
         <f t="shared" si="8"/>
         <v>168</v>
       </c>
-      <c r="W9" s="36"/>
-      <c r="X9" s="36"/>
-      <c r="Y9" s="37">
+      <c r="W9" s="37"/>
+      <c r="X9" s="37"/>
+      <c r="Y9" s="38">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="Z9" s="36"/>
+      <c r="Z9" s="37"/>
       <c r="AD9" s="7" t="s">
         <v>58</v>
       </c>
@@ -2794,28 +2869,28 @@
       <c r="D10" s="9">
         <v>0</v>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F10" s="27">
+      <c r="F10" s="28">
         <v>0.2</v>
       </c>
-      <c r="G10" s="28">
+      <c r="G10" s="29">
         <v>0.8</v>
       </c>
-      <c r="H10" s="25">
+      <c r="H10" s="26">
         <v>5</v>
       </c>
-      <c r="I10" s="25">
+      <c r="I10" s="26">
         <f t="shared" si="1"/>
         <v>1.1</v>
       </c>
-      <c r="J10" s="25">
+      <c r="J10" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K10" s="25">
+      <c r="K10" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -2826,33 +2901,33 @@
       <c r="N10" s="17">
         <v>10</v>
       </c>
-      <c r="O10" s="33">
+      <c r="O10" s="34">
         <f t="shared" si="4"/>
         <v>36.57</v>
       </c>
-      <c r="Q10" s="34">
+      <c r="Q10" s="35">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="R10" s="34">
+      <c r="R10" s="35">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T10" s="7">
         <v>32</v>
       </c>
-      <c r="U10" s="36"/>
-      <c r="V10" s="37">
+      <c r="U10" s="37"/>
+      <c r="V10" s="38">
         <f t="shared" si="8"/>
         <v>96</v>
       </c>
-      <c r="W10" s="36"/>
-      <c r="X10" s="36"/>
-      <c r="Y10" s="37">
+      <c r="W10" s="37"/>
+      <c r="X10" s="37"/>
+      <c r="Y10" s="38">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="Z10" s="36"/>
+      <c r="Z10" s="37"/>
       <c r="AD10" s="7" t="s">
         <v>62</v>
       </c>
@@ -2882,28 +2957,28 @@
       <c r="D11" s="9">
         <v>0</v>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F11" s="27">
+      <c r="F11" s="28">
         <v>3.7</v>
       </c>
-      <c r="G11" s="28">
+      <c r="G11" s="29">
         <v>4.2</v>
       </c>
-      <c r="H11" s="25">
+      <c r="H11" s="26">
         <v>5.5</v>
       </c>
-      <c r="I11" s="25">
+      <c r="I11" s="26">
         <f t="shared" si="1"/>
         <v>5.775</v>
       </c>
-      <c r="J11" s="25">
+      <c r="J11" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K11" s="25">
+      <c r="K11" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -2914,33 +2989,33 @@
       <c r="N11" s="17">
         <v>13.38</v>
       </c>
-      <c r="O11" s="33">
+      <c r="O11" s="34">
         <f t="shared" si="4"/>
         <v>49.49</v>
       </c>
-      <c r="Q11" s="34">
+      <c r="Q11" s="35">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="R11" s="34">
+      <c r="R11" s="35">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T11" s="7">
         <v>24</v>
       </c>
-      <c r="U11" s="36"/>
-      <c r="V11" s="37">
+      <c r="U11" s="37"/>
+      <c r="V11" s="38">
         <f t="shared" si="8"/>
         <v>360</v>
       </c>
-      <c r="W11" s="36"/>
-      <c r="X11" s="36"/>
-      <c r="Y11" s="37">
+      <c r="W11" s="37"/>
+      <c r="X11" s="37"/>
+      <c r="Y11" s="38">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="Z11" s="36"/>
+      <c r="Z11" s="37"/>
       <c r="AD11" s="7" t="s">
         <v>66</v>
       </c>
@@ -2970,29 +3045,29 @@
       <c r="D12" s="9">
         <v>0</v>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F12" s="27">
+      <c r="F12" s="28">
         <v>0.1</v>
       </c>
-      <c r="G12" s="28">
+      <c r="G12" s="29">
         <v>0.2</v>
       </c>
-      <c r="H12" s="25">
+      <c r="H12" s="26">
         <f t="shared" si="7"/>
         <v>0.1375</v>
       </c>
-      <c r="I12" s="25">
+      <c r="I12" s="26">
         <f t="shared" si="1"/>
         <v>0.275</v>
       </c>
-      <c r="J12" s="25">
+      <c r="J12" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K12" s="25">
+      <c r="K12" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -3003,33 +3078,33 @@
       <c r="N12" s="17">
         <v>13.38</v>
       </c>
-      <c r="O12" s="33">
+      <c r="O12" s="34">
         <f t="shared" si="4"/>
         <v>53.18</v>
       </c>
-      <c r="Q12" s="34">
+      <c r="Q12" s="35">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="R12" s="34">
+      <c r="R12" s="35">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T12" s="7">
         <v>12</v>
       </c>
-      <c r="U12" s="36"/>
-      <c r="V12" s="37">
+      <c r="U12" s="37"/>
+      <c r="V12" s="38">
         <f t="shared" si="8"/>
         <v>24</v>
       </c>
-      <c r="W12" s="36"/>
-      <c r="X12" s="36"/>
-      <c r="Y12" s="37">
+      <c r="W12" s="37"/>
+      <c r="X12" s="37"/>
+      <c r="Y12" s="38">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="Z12" s="36"/>
+      <c r="Z12" s="37"/>
       <c r="AD12" s="7" t="s">
         <v>70</v>
       </c>
@@ -3059,29 +3134,29 @@
       <c r="D13" s="9">
         <v>0</v>
       </c>
-      <c r="E13" s="26">
+      <c r="E13" s="27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F13" s="27">
+      <c r="F13" s="28">
         <v>0.8</v>
       </c>
-      <c r="G13" s="28">
+      <c r="G13" s="29">
         <v>1.1</v>
       </c>
-      <c r="H13" s="25">
+      <c r="H13" s="26">
         <f t="shared" si="7"/>
         <v>1.1</v>
       </c>
-      <c r="I13" s="25">
+      <c r="I13" s="26">
         <f t="shared" si="1"/>
         <v>1.5125</v>
       </c>
-      <c r="J13" s="25">
+      <c r="J13" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K13" s="25">
+      <c r="K13" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -3092,33 +3167,33 @@
       <c r="N13" s="17">
         <v>10.47</v>
       </c>
-      <c r="O13" s="33">
+      <c r="O13" s="34">
         <f t="shared" si="4"/>
         <v>44.18</v>
       </c>
-      <c r="Q13" s="34">
+      <c r="Q13" s="35">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="R13" s="34">
+      <c r="R13" s="35">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T13" s="7">
         <v>15</v>
       </c>
-      <c r="U13" s="36"/>
-      <c r="V13" s="37">
+      <c r="U13" s="37"/>
+      <c r="V13" s="38">
         <f t="shared" si="8"/>
         <v>105</v>
       </c>
-      <c r="W13" s="36"/>
-      <c r="X13" s="36"/>
-      <c r="Y13" s="37">
+      <c r="W13" s="37"/>
+      <c r="X13" s="37"/>
+      <c r="Y13" s="38">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="Z13" s="36"/>
+      <c r="Z13" s="37"/>
       <c r="AD13" s="7" t="s">
         <v>74</v>
       </c>
@@ -3148,29 +3223,29 @@
       <c r="D14" s="9">
         <v>0</v>
       </c>
-      <c r="E14" s="26">
+      <c r="E14" s="27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F14" s="27">
+      <c r="F14" s="28">
         <v>2.5</v>
       </c>
-      <c r="G14" s="28">
+      <c r="G14" s="29">
         <v>2</v>
       </c>
-      <c r="H14" s="25">
+      <c r="H14" s="26">
         <f t="shared" si="7"/>
         <v>3.4375</v>
       </c>
-      <c r="I14" s="25">
+      <c r="I14" s="26">
         <f t="shared" si="1"/>
         <v>3.4375</v>
       </c>
-      <c r="J14" s="25">
+      <c r="J14" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K14" s="25">
+      <c r="K14" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -3181,33 +3256,33 @@
       <c r="N14" s="17">
         <v>13.38</v>
       </c>
-      <c r="O14" s="33">
+      <c r="O14" s="34">
         <f t="shared" si="4"/>
         <v>53.18</v>
       </c>
-      <c r="Q14" s="34">
+      <c r="Q14" s="35">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="R14" s="34">
+      <c r="R14" s="35">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T14" s="7">
         <v>12</v>
       </c>
-      <c r="U14" s="36"/>
-      <c r="V14" s="37">
+      <c r="U14" s="37"/>
+      <c r="V14" s="38">
         <f t="shared" si="8"/>
         <v>216</v>
       </c>
-      <c r="W14" s="36"/>
-      <c r="X14" s="36"/>
-      <c r="Y14" s="37">
+      <c r="W14" s="37"/>
+      <c r="X14" s="37"/>
+      <c r="Y14" s="38">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="Z14" s="36"/>
+      <c r="Z14" s="37"/>
       <c r="AD14" s="7" t="s">
         <v>78</v>
       </c>
@@ -3237,7 +3312,7 @@
       <c r="D15" s="9">
         <v>0</v>
       </c>
-      <c r="E15" s="26">
+      <c r="E15" s="27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -3247,18 +3322,18 @@
       <c r="G15" s="7">
         <v>0.1</v>
       </c>
-      <c r="H15" s="25">
+      <c r="H15" s="26">
         <v>3</v>
       </c>
-      <c r="I15" s="25">
+      <c r="I15" s="26">
         <f t="shared" si="1"/>
         <v>0.55</v>
       </c>
-      <c r="J15" s="25">
+      <c r="J15" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K15" s="25">
+      <c r="K15" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -3269,33 +3344,33 @@
       <c r="N15" s="17">
         <v>10</v>
       </c>
-      <c r="O15" s="33">
+      <c r="O15" s="34">
         <f t="shared" si="4"/>
         <v>34.37</v>
       </c>
-      <c r="Q15" s="34">
+      <c r="Q15" s="35">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="R15" s="34">
+      <c r="R15" s="35">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T15" s="7">
         <v>16</v>
       </c>
-      <c r="U15" s="36"/>
-      <c r="V15" s="37">
+      <c r="U15" s="37"/>
+      <c r="V15" s="38">
         <f t="shared" si="8"/>
         <v>48</v>
       </c>
-      <c r="W15" s="36"/>
-      <c r="X15" s="36"/>
-      <c r="Y15" s="37">
+      <c r="W15" s="37"/>
+      <c r="X15" s="37"/>
+      <c r="Y15" s="38">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="Z15" s="36"/>
+      <c r="Z15" s="37"/>
       <c r="AD15" s="7" t="s">
         <v>82</v>
       </c>
@@ -3325,28 +3400,28 @@
       <c r="D16" s="9">
         <v>0</v>
       </c>
-      <c r="E16" s="26">
+      <c r="E16" s="27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F16" s="27">
+      <c r="F16" s="28">
         <v>1.4</v>
       </c>
-      <c r="G16" s="28">
+      <c r="G16" s="29">
         <v>1.4</v>
       </c>
-      <c r="H16" s="25">
+      <c r="H16" s="26">
         <v>1.9</v>
       </c>
-      <c r="I16" s="25">
+      <c r="I16" s="26">
         <f t="shared" si="1"/>
         <v>1.925</v>
       </c>
-      <c r="J16" s="25">
+      <c r="J16" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K16" s="25">
+      <c r="K16" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -3357,33 +3432,33 @@
       <c r="N16" s="17">
         <v>10</v>
       </c>
-      <c r="O16" s="33">
+      <c r="O16" s="34">
         <f t="shared" si="4"/>
         <v>34.37</v>
       </c>
-      <c r="Q16" s="34">
+      <c r="Q16" s="35">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="R16" s="34">
+      <c r="R16" s="35">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T16" s="7">
         <v>16</v>
       </c>
-      <c r="U16" s="37">
+      <c r="U16" s="38">
         <f t="shared" ref="U16:U29" si="10">CEILING(MAX(0,90-MAX(K16,60))*I16/T16,1)*T16</f>
         <v>64</v>
       </c>
-      <c r="V16" s="36"/>
-      <c r="W16" s="36"/>
-      <c r="X16" s="37">
+      <c r="V16" s="37"/>
+      <c r="W16" s="37"/>
+      <c r="X16" s="38">
         <f t="shared" ref="X16:X29" si="11">MIN(CEILING(MAX(0,70-MAX(J16,30))*I16/T16,1)*T16,D16)</f>
         <v>0</v>
       </c>
-      <c r="Y16" s="36"/>
-      <c r="Z16" s="36"/>
+      <c r="Y16" s="37"/>
+      <c r="Z16" s="37"/>
       <c r="AD16" s="7" t="s">
         <v>86</v>
       </c>
@@ -3413,28 +3488,28 @@
       <c r="D17" s="9">
         <v>0</v>
       </c>
-      <c r="E17" s="26">
+      <c r="E17" s="27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F17" s="27">
+      <c r="F17" s="28">
         <v>1</v>
       </c>
-      <c r="G17" s="28">
+      <c r="G17" s="29">
         <v>0.4</v>
       </c>
-      <c r="H17" s="25">
+      <c r="H17" s="26">
         <v>6</v>
       </c>
-      <c r="I17" s="25">
+      <c r="I17" s="26">
         <f t="shared" si="1"/>
         <v>1.375</v>
       </c>
-      <c r="J17" s="25">
+      <c r="J17" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K17" s="25">
+      <c r="K17" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -3445,33 +3520,33 @@
       <c r="N17" s="17">
         <v>6</v>
       </c>
-      <c r="O17" s="33">
+      <c r="O17" s="34">
         <f t="shared" si="4"/>
         <v>25.43</v>
       </c>
-      <c r="Q17" s="34">
+      <c r="Q17" s="35">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="R17" s="34">
+      <c r="R17" s="35">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T17" s="7">
         <v>20</v>
       </c>
-      <c r="U17" s="37">
+      <c r="U17" s="38">
         <f t="shared" si="10"/>
         <v>60</v>
       </c>
-      <c r="V17" s="36"/>
-      <c r="W17" s="36"/>
-      <c r="X17" s="37">
+      <c r="V17" s="37"/>
+      <c r="W17" s="37"/>
+      <c r="X17" s="38">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Y17" s="36"/>
-      <c r="Z17" s="36"/>
+      <c r="Y17" s="37"/>
+      <c r="Z17" s="37"/>
       <c r="AD17" s="7" t="s">
         <v>90</v>
       </c>
@@ -3501,29 +3576,29 @@
       <c r="D18" s="9">
         <v>0</v>
       </c>
-      <c r="E18" s="26">
+      <c r="E18" s="27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F18" s="27">
+      <c r="F18" s="28">
         <v>1</v>
       </c>
-      <c r="G18" s="28">
+      <c r="G18" s="29">
         <v>0.3</v>
       </c>
-      <c r="H18" s="25">
+      <c r="H18" s="26">
         <f t="shared" ref="H18:H21" si="12">MAX(E18,F18)*1.375</f>
         <v>1.375</v>
       </c>
-      <c r="I18" s="25">
+      <c r="I18" s="26">
         <f t="shared" si="1"/>
         <v>1.375</v>
       </c>
-      <c r="J18" s="25">
+      <c r="J18" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K18" s="25">
+      <c r="K18" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -3534,33 +3609,33 @@
       <c r="N18" s="17">
         <v>13.38</v>
       </c>
-      <c r="O18" s="33">
+      <c r="O18" s="34">
         <f t="shared" si="4"/>
         <v>49.49</v>
       </c>
-      <c r="Q18" s="34">
+      <c r="Q18" s="35">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="R18" s="34">
+      <c r="R18" s="35">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T18" s="7">
         <v>12</v>
       </c>
-      <c r="U18" s="37">
+      <c r="U18" s="38">
         <f t="shared" si="10"/>
         <v>48</v>
       </c>
-      <c r="V18" s="36"/>
-      <c r="W18" s="36"/>
-      <c r="X18" s="37">
+      <c r="V18" s="37"/>
+      <c r="W18" s="37"/>
+      <c r="X18" s="38">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Y18" s="36"/>
-      <c r="Z18" s="36"/>
+      <c r="Y18" s="37"/>
+      <c r="Z18" s="37"/>
       <c r="AD18" s="7" t="s">
         <v>94</v>
       </c>
@@ -3590,28 +3665,28 @@
       <c r="D19" s="9">
         <v>0</v>
       </c>
-      <c r="E19" s="26">
+      <c r="E19" s="27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F19" s="27">
+      <c r="F19" s="28">
         <v>0.5</v>
       </c>
-      <c r="G19" s="28">
+      <c r="G19" s="29">
         <v>0.9</v>
       </c>
-      <c r="H19" s="25">
+      <c r="H19" s="26">
         <v>1.4</v>
       </c>
-      <c r="I19" s="25">
+      <c r="I19" s="26">
         <f t="shared" ref="I19:I41" si="13">MAX(F19,G19)*1.375</f>
         <v>1.2375</v>
       </c>
-      <c r="J19" s="25">
+      <c r="J19" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K19" s="25">
+      <c r="K19" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -3622,33 +3697,33 @@
       <c r="N19" s="17">
         <v>10</v>
       </c>
-      <c r="O19" s="33">
+      <c r="O19" s="34">
         <f t="shared" si="4"/>
         <v>34.37</v>
       </c>
-      <c r="Q19" s="34">
+      <c r="Q19" s="35">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="R19" s="34">
+      <c r="R19" s="35">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T19" s="7">
         <v>16</v>
       </c>
-      <c r="U19" s="37">
+      <c r="U19" s="38">
         <f t="shared" si="10"/>
         <v>48</v>
       </c>
-      <c r="V19" s="36"/>
-      <c r="W19" s="36"/>
-      <c r="X19" s="37">
+      <c r="V19" s="37"/>
+      <c r="W19" s="37"/>
+      <c r="X19" s="38">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Y19" s="36"/>
-      <c r="Z19" s="36"/>
+      <c r="Y19" s="37"/>
+      <c r="Z19" s="37"/>
       <c r="AD19" s="7" t="s">
         <v>98</v>
       </c>
@@ -3678,29 +3753,29 @@
       <c r="D20" s="9">
         <v>0</v>
       </c>
-      <c r="E20" s="26">
+      <c r="E20" s="27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F20" s="27">
-        <v>0</v>
-      </c>
-      <c r="G20" s="28">
+      <c r="F20" s="28">
+        <v>0</v>
+      </c>
+      <c r="G20" s="29">
         <v>0.4</v>
       </c>
-      <c r="H20" s="25">
+      <c r="H20" s="26">
         <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="I20" s="25">
+      <c r="I20" s="26">
         <f t="shared" si="13"/>
         <v>0.55</v>
       </c>
-      <c r="J20" s="25">
+      <c r="J20" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K20" s="25">
+      <c r="K20" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -3711,33 +3786,33 @@
       <c r="N20" s="17">
         <v>13.38</v>
       </c>
-      <c r="O20" s="33">
+      <c r="O20" s="34">
         <f t="shared" si="4"/>
         <v>49.49</v>
       </c>
-      <c r="Q20" s="34">
+      <c r="Q20" s="35">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="R20" s="34">
+      <c r="R20" s="35">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T20" s="7">
         <v>12</v>
       </c>
-      <c r="U20" s="37">
+      <c r="U20" s="38">
         <f t="shared" si="10"/>
         <v>24</v>
       </c>
-      <c r="V20" s="36"/>
-      <c r="W20" s="36"/>
-      <c r="X20" s="37">
+      <c r="V20" s="37"/>
+      <c r="W20" s="37"/>
+      <c r="X20" s="38">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Y20" s="36"/>
-      <c r="Z20" s="36"/>
+      <c r="Y20" s="37"/>
+      <c r="Z20" s="37"/>
       <c r="AD20" s="7" t="s">
         <v>102</v>
       </c>
@@ -3767,29 +3842,29 @@
       <c r="D21" s="9">
         <v>0</v>
       </c>
-      <c r="E21" s="26">
+      <c r="E21" s="27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F21" s="27">
+      <c r="F21" s="28">
         <v>1.7</v>
       </c>
-      <c r="G21" s="28">
+      <c r="G21" s="29">
         <v>1.8</v>
       </c>
-      <c r="H21" s="25">
+      <c r="H21" s="26">
         <f t="shared" si="12"/>
         <v>2.3375</v>
       </c>
-      <c r="I21" s="25">
+      <c r="I21" s="26">
         <f t="shared" si="13"/>
         <v>2.475</v>
       </c>
-      <c r="J21" s="25">
+      <c r="J21" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K21" s="25">
+      <c r="K21" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -3800,33 +3875,33 @@
       <c r="N21" s="17">
         <v>6.98</v>
       </c>
-      <c r="O21" s="33">
+      <c r="O21" s="34">
         <f t="shared" si="4"/>
         <v>29.72</v>
       </c>
-      <c r="Q21" s="34">
+      <c r="Q21" s="35">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="R21" s="34">
+      <c r="R21" s="35">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T21" s="7">
         <v>21</v>
       </c>
-      <c r="U21" s="37">
+      <c r="U21" s="38">
         <f t="shared" si="10"/>
         <v>84</v>
       </c>
-      <c r="V21" s="36"/>
-      <c r="W21" s="36"/>
-      <c r="X21" s="37">
+      <c r="V21" s="37"/>
+      <c r="W21" s="37"/>
+      <c r="X21" s="38">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Y21" s="36"/>
-      <c r="Z21" s="36"/>
+      <c r="Y21" s="37"/>
+      <c r="Z21" s="37"/>
       <c r="AD21" s="7" t="s">
         <v>106</v>
       </c>
@@ -3856,28 +3931,28 @@
       <c r="D22" s="9">
         <v>0</v>
       </c>
-      <c r="E22" s="26">
+      <c r="E22" s="27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F22" s="27">
+      <c r="F22" s="28">
         <v>0.5</v>
       </c>
-      <c r="G22" s="28">
+      <c r="G22" s="29">
         <v>0.5</v>
       </c>
-      <c r="H22" s="25">
+      <c r="H22" s="26">
         <v>2</v>
       </c>
-      <c r="I22" s="25">
+      <c r="I22" s="26">
         <f t="shared" si="13"/>
         <v>0.6875</v>
       </c>
-      <c r="J22" s="25">
+      <c r="J22" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K22" s="25">
+      <c r="K22" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -3888,33 +3963,33 @@
       <c r="N22" s="17">
         <v>9</v>
       </c>
-      <c r="O22" s="33">
+      <c r="O22" s="34">
         <f t="shared" si="4"/>
         <v>37.52</v>
       </c>
-      <c r="Q22" s="34">
+      <c r="Q22" s="35">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="R22" s="34">
+      <c r="R22" s="35">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T22" s="7">
         <v>14</v>
       </c>
-      <c r="U22" s="37">
+      <c r="U22" s="38">
         <f t="shared" si="10"/>
         <v>28</v>
       </c>
-      <c r="V22" s="36"/>
-      <c r="W22" s="36"/>
-      <c r="X22" s="37">
+      <c r="V22" s="37"/>
+      <c r="W22" s="37"/>
+      <c r="X22" s="38">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Y22" s="36"/>
-      <c r="Z22" s="36"/>
+      <c r="Y22" s="37"/>
+      <c r="Z22" s="37"/>
       <c r="AD22" s="7" t="s">
         <v>110</v>
       </c>
@@ -3944,29 +4019,29 @@
       <c r="D23" s="9">
         <v>0</v>
       </c>
-      <c r="E23" s="26">
+      <c r="E23" s="27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F23" s="27">
+      <c r="F23" s="28">
         <v>0.5</v>
       </c>
-      <c r="G23" s="28">
+      <c r="G23" s="29">
         <v>0.7</v>
       </c>
-      <c r="H23" s="25">
+      <c r="H23" s="26">
         <f>MAX(E23,F23)*1.375</f>
         <v>0.6875</v>
       </c>
-      <c r="I23" s="25">
+      <c r="I23" s="26">
         <f t="shared" si="13"/>
         <v>0.9625</v>
       </c>
-      <c r="J23" s="25">
+      <c r="J23" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K23" s="25">
+      <c r="K23" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -3977,33 +4052,33 @@
       <c r="N23" s="17">
         <v>10</v>
       </c>
-      <c r="O23" s="33">
+      <c r="O23" s="34">
         <f t="shared" si="4"/>
         <v>34.37</v>
       </c>
-      <c r="Q23" s="34">
+      <c r="Q23" s="35">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="R23" s="34">
+      <c r="R23" s="35">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T23" s="7">
         <v>16</v>
       </c>
-      <c r="U23" s="37">
+      <c r="U23" s="38">
         <f t="shared" si="10"/>
         <v>32</v>
       </c>
-      <c r="V23" s="36"/>
-      <c r="W23" s="36"/>
-      <c r="X23" s="37">
+      <c r="V23" s="37"/>
+      <c r="W23" s="37"/>
+      <c r="X23" s="38">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Y23" s="36"/>
-      <c r="Z23" s="36"/>
+      <c r="Y23" s="37"/>
+      <c r="Z23" s="37"/>
       <c r="AD23" s="7" t="s">
         <v>114</v>
       </c>
@@ -4033,29 +4108,29 @@
       <c r="D24" s="9">
         <v>0</v>
       </c>
-      <c r="E24" s="26">
+      <c r="E24" s="27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F24" s="28">
+      <c r="F24" s="29">
         <v>0.7</v>
       </c>
-      <c r="G24" s="28">
+      <c r="G24" s="29">
         <v>1</v>
       </c>
-      <c r="H24" s="25">
+      <c r="H24" s="26">
         <f>MAX(E24,F24)*1.375</f>
         <v>0.9625</v>
       </c>
-      <c r="I24" s="25">
+      <c r="I24" s="26">
         <f t="shared" si="13"/>
         <v>1.375</v>
       </c>
-      <c r="J24" s="25">
+      <c r="J24" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K24" s="25">
+      <c r="K24" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4066,33 +4141,33 @@
       <c r="N24" s="17">
         <v>10</v>
       </c>
-      <c r="O24" s="33">
+      <c r="O24" s="34">
         <f t="shared" si="4"/>
         <v>34.37</v>
       </c>
-      <c r="Q24" s="34">
+      <c r="Q24" s="35">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="R24" s="34">
+      <c r="R24" s="35">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T24" s="7">
         <v>16</v>
       </c>
-      <c r="U24" s="37">
+      <c r="U24" s="38">
         <f t="shared" si="10"/>
         <v>48</v>
       </c>
-      <c r="V24" s="36"/>
-      <c r="W24" s="36"/>
-      <c r="X24" s="37">
+      <c r="V24" s="37"/>
+      <c r="W24" s="37"/>
+      <c r="X24" s="38">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Y24" s="36"/>
-      <c r="Z24" s="36"/>
+      <c r="Y24" s="37"/>
+      <c r="Z24" s="37"/>
       <c r="AD24" s="7" t="s">
         <v>118</v>
       </c>
@@ -4122,28 +4197,28 @@
       <c r="D25" s="9">
         <v>0</v>
       </c>
-      <c r="E25" s="26">
+      <c r="E25" s="27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F25" s="28">
+      <c r="F25" s="29">
         <v>1.2</v>
       </c>
-      <c r="G25" s="28">
+      <c r="G25" s="29">
         <v>1.4</v>
       </c>
-      <c r="H25" s="25">
+      <c r="H25" s="26">
         <v>2.5</v>
       </c>
-      <c r="I25" s="25">
+      <c r="I25" s="26">
         <f t="shared" si="13"/>
         <v>1.925</v>
       </c>
-      <c r="J25" s="25">
+      <c r="J25" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K25" s="25">
+      <c r="K25" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4154,33 +4229,33 @@
       <c r="N25" s="17">
         <v>6</v>
       </c>
-      <c r="O25" s="33">
+      <c r="O25" s="34">
         <f t="shared" si="4"/>
         <v>25.43</v>
       </c>
-      <c r="Q25" s="34">
+      <c r="Q25" s="35">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="R25" s="34">
+      <c r="R25" s="35">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T25" s="7">
         <v>20</v>
       </c>
-      <c r="U25" s="37">
+      <c r="U25" s="38">
         <f t="shared" si="10"/>
         <v>60</v>
       </c>
-      <c r="V25" s="36"/>
-      <c r="W25" s="36"/>
-      <c r="X25" s="37">
+      <c r="V25" s="37"/>
+      <c r="W25" s="37"/>
+      <c r="X25" s="38">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Y25" s="36"/>
-      <c r="Z25" s="36"/>
+      <c r="Y25" s="37"/>
+      <c r="Z25" s="37"/>
       <c r="AD25" s="7" t="s">
         <v>122</v>
       </c>
@@ -4210,28 +4285,28 @@
       <c r="D26" s="9">
         <v>0</v>
       </c>
-      <c r="E26" s="26">
+      <c r="E26" s="27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F26" s="28">
+      <c r="F26" s="29">
         <v>0.7</v>
       </c>
-      <c r="G26" s="28">
+      <c r="G26" s="29">
         <v>0.7</v>
       </c>
-      <c r="H26" s="25">
+      <c r="H26" s="26">
         <v>4</v>
       </c>
-      <c r="I26" s="25">
+      <c r="I26" s="26">
         <f t="shared" si="13"/>
         <v>0.9625</v>
       </c>
-      <c r="J26" s="25">
+      <c r="J26" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K26" s="25">
+      <c r="K26" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4242,33 +4317,33 @@
       <c r="N26" s="17">
         <v>6.98</v>
       </c>
-      <c r="O26" s="33">
+      <c r="O26" s="34">
         <f t="shared" si="4"/>
         <v>29.72</v>
       </c>
-      <c r="Q26" s="34">
+      <c r="Q26" s="35">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="R26" s="34">
+      <c r="R26" s="35">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T26" s="7">
         <v>21</v>
       </c>
-      <c r="U26" s="37">
+      <c r="U26" s="38">
         <f t="shared" si="10"/>
         <v>42</v>
       </c>
-      <c r="V26" s="36"/>
-      <c r="W26" s="36"/>
-      <c r="X26" s="37">
+      <c r="V26" s="37"/>
+      <c r="W26" s="37"/>
+      <c r="X26" s="38">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Y26" s="36"/>
-      <c r="Z26" s="36"/>
+      <c r="Y26" s="37"/>
+      <c r="Z26" s="37"/>
       <c r="AD26" s="7" t="s">
         <v>126</v>
       </c>
@@ -4298,29 +4373,29 @@
       <c r="D27" s="9">
         <v>0</v>
       </c>
-      <c r="E27" s="26">
+      <c r="E27" s="27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F27" s="28">
+      <c r="F27" s="29">
         <v>1.5</v>
       </c>
-      <c r="G27" s="28">
+      <c r="G27" s="29">
         <v>1.2</v>
       </c>
-      <c r="H27" s="25">
+      <c r="H27" s="26">
         <f>MAX(E27,F27)*1.375</f>
         <v>2.0625</v>
       </c>
-      <c r="I27" s="25">
+      <c r="I27" s="26">
         <f t="shared" si="13"/>
         <v>2.0625</v>
       </c>
-      <c r="J27" s="25">
+      <c r="J27" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K27" s="25">
+      <c r="K27" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4331,33 +4406,33 @@
       <c r="N27" s="17">
         <v>10</v>
       </c>
-      <c r="O27" s="33">
+      <c r="O27" s="34">
         <f t="shared" si="4"/>
         <v>34.37</v>
       </c>
-      <c r="Q27" s="34">
+      <c r="Q27" s="35">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="R27" s="34">
+      <c r="R27" s="35">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T27" s="7">
         <v>16</v>
       </c>
-      <c r="U27" s="37">
+      <c r="U27" s="38">
         <f t="shared" si="10"/>
         <v>64</v>
       </c>
-      <c r="V27" s="36"/>
-      <c r="W27" s="36"/>
-      <c r="X27" s="37">
+      <c r="V27" s="37"/>
+      <c r="W27" s="37"/>
+      <c r="X27" s="38">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Y27" s="36"/>
-      <c r="Z27" s="36"/>
+      <c r="Y27" s="37"/>
+      <c r="Z27" s="37"/>
       <c r="AD27" s="7" t="s">
         <v>130</v>
       </c>
@@ -4387,29 +4462,29 @@
       <c r="D28" s="9">
         <v>0</v>
       </c>
-      <c r="E28" s="26">
+      <c r="E28" s="27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F28" s="27">
+      <c r="F28" s="28">
         <v>1.1</v>
       </c>
-      <c r="G28" s="28">
+      <c r="G28" s="29">
         <v>0.5</v>
       </c>
-      <c r="H28" s="25">
+      <c r="H28" s="26">
         <f>MAX(E28,F28)*1.375</f>
         <v>1.5125</v>
       </c>
-      <c r="I28" s="25">
+      <c r="I28" s="26">
         <f t="shared" si="13"/>
         <v>1.5125</v>
       </c>
-      <c r="J28" s="25">
+      <c r="J28" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K28" s="25">
+      <c r="K28" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4420,33 +4495,33 @@
       <c r="N28" s="17">
         <v>13.38</v>
       </c>
-      <c r="O28" s="33">
+      <c r="O28" s="34">
         <f t="shared" si="4"/>
         <v>49.49</v>
       </c>
-      <c r="Q28" s="34">
+      <c r="Q28" s="35">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="R28" s="34">
+      <c r="R28" s="35">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T28" s="7">
         <v>12</v>
       </c>
-      <c r="U28" s="37">
+      <c r="U28" s="38">
         <f t="shared" si="10"/>
         <v>48</v>
       </c>
-      <c r="V28" s="36"/>
-      <c r="W28" s="36"/>
-      <c r="X28" s="37">
+      <c r="V28" s="37"/>
+      <c r="W28" s="37"/>
+      <c r="X28" s="38">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Y28" s="36"/>
-      <c r="Z28" s="36"/>
+      <c r="Y28" s="37"/>
+      <c r="Z28" s="37"/>
       <c r="AD28" s="7" t="s">
         <v>134</v>
       </c>
@@ -4476,29 +4551,29 @@
       <c r="D29" s="9">
         <v>0</v>
       </c>
-      <c r="E29" s="26">
+      <c r="E29" s="27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F29" s="27">
+      <c r="F29" s="28">
         <v>0.8</v>
       </c>
-      <c r="G29" s="28">
+      <c r="G29" s="29">
         <v>1</v>
       </c>
-      <c r="H29" s="25">
+      <c r="H29" s="26">
         <f>MAX(E29,F29)*1.375</f>
         <v>1.1</v>
       </c>
-      <c r="I29" s="25">
+      <c r="I29" s="26">
         <f t="shared" si="13"/>
         <v>1.375</v>
       </c>
-      <c r="J29" s="25">
+      <c r="J29" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K29" s="25">
+      <c r="K29" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4509,33 +4584,33 @@
       <c r="N29" s="17">
         <v>10</v>
       </c>
-      <c r="O29" s="33">
+      <c r="O29" s="34">
         <f t="shared" si="4"/>
         <v>34.37</v>
       </c>
-      <c r="Q29" s="34">
+      <c r="Q29" s="35">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="R29" s="34">
+      <c r="R29" s="35">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T29" s="7">
         <v>16</v>
       </c>
-      <c r="U29" s="37">
+      <c r="U29" s="38">
         <f t="shared" si="10"/>
         <v>48</v>
       </c>
-      <c r="V29" s="36"/>
-      <c r="W29" s="36"/>
-      <c r="X29" s="37">
+      <c r="V29" s="37"/>
+      <c r="W29" s="37"/>
+      <c r="X29" s="38">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="Y29" s="36"/>
-      <c r="Z29" s="36"/>
+      <c r="Y29" s="37"/>
+      <c r="Z29" s="37"/>
       <c r="AD29" s="7" t="s">
         <v>138</v>
       </c>
@@ -4565,29 +4640,29 @@
       <c r="D30" s="9">
         <v>0</v>
       </c>
-      <c r="E30" s="29">
+      <c r="E30" s="30">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F30" s="30">
+      <c r="F30" s="31">
         <v>0.1</v>
       </c>
-      <c r="G30" s="31">
-        <v>0</v>
-      </c>
-      <c r="H30" s="25">
+      <c r="G30" s="32">
+        <v>0</v>
+      </c>
+      <c r="H30" s="26">
         <f>MAX(E30,F30)*1.375</f>
         <v>0.1375</v>
       </c>
-      <c r="I30" s="25">
+      <c r="I30" s="26">
         <f t="shared" si="13"/>
         <v>0.1375</v>
       </c>
-      <c r="J30" s="25">
+      <c r="J30" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K30" s="25">
+      <c r="K30" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4598,33 +4673,33 @@
       <c r="N30" s="17">
         <v>10</v>
       </c>
-      <c r="O30" s="33">
+      <c r="O30" s="34">
         <f t="shared" si="4"/>
         <v>36.57</v>
       </c>
-      <c r="Q30" s="34">
+      <c r="Q30" s="35">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="R30" s="34">
+      <c r="R30" s="35">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T30" s="7">
         <v>16</v>
       </c>
-      <c r="U30" s="37">
+      <c r="U30" s="38">
         <f t="shared" ref="U30:U44" si="14">CEILING(MAX(0,90-MAX(K30,60))*I30/T30,1)*T30</f>
         <v>16</v>
       </c>
-      <c r="V30" s="36"/>
-      <c r="W30" s="36"/>
-      <c r="X30" s="37">
+      <c r="V30" s="37"/>
+      <c r="W30" s="37"/>
+      <c r="X30" s="38">
         <f t="shared" ref="X30:X44" si="15">MIN(CEILING(MAX(0,70-MAX(J30,30))*I30/T30,1)*T30,D30)</f>
         <v>0</v>
       </c>
-      <c r="Y30" s="36"/>
-      <c r="Z30" s="36"/>
+      <c r="Y30" s="37"/>
+      <c r="Z30" s="37"/>
       <c r="AD30" s="7" t="s">
         <v>142</v>
       </c>
@@ -4654,29 +4729,29 @@
       <c r="D31" s="9">
         <v>0</v>
       </c>
-      <c r="E31" s="29">
+      <c r="E31" s="30">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F31" s="27">
+      <c r="F31" s="28">
         <v>0.1</v>
       </c>
-      <c r="G31" s="28">
+      <c r="G31" s="29">
         <v>0.1</v>
       </c>
-      <c r="H31" s="25">
+      <c r="H31" s="26">
         <f>MAX(E31,F31)*1.375</f>
         <v>0.1375</v>
       </c>
-      <c r="I31" s="25">
+      <c r="I31" s="26">
         <f t="shared" si="13"/>
         <v>0.1375</v>
       </c>
-      <c r="J31" s="25">
+      <c r="J31" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K31" s="25">
+      <c r="K31" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4687,33 +4762,33 @@
       <c r="N31" s="17" t="s">
         <v>147</v>
       </c>
-      <c r="O31" s="33">
+      <c r="O31" s="34">
         <f t="shared" si="4"/>
         <v>30</v>
       </c>
-      <c r="Q31" s="34">
+      <c r="Q31" s="35">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="R31" s="34">
+      <c r="R31" s="35">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T31" s="7">
         <v>30</v>
       </c>
-      <c r="U31" s="37">
+      <c r="U31" s="38">
         <f t="shared" si="14"/>
         <v>30</v>
       </c>
-      <c r="V31" s="36"/>
-      <c r="W31" s="36"/>
-      <c r="X31" s="37">
+      <c r="V31" s="37"/>
+      <c r="W31" s="37"/>
+      <c r="X31" s="38">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="Y31" s="36"/>
-      <c r="Z31" s="36"/>
+      <c r="Y31" s="37"/>
+      <c r="Z31" s="37"/>
       <c r="AD31" s="7" t="s">
         <v>148</v>
       </c>
@@ -4743,7 +4818,7 @@
       <c r="D32" s="9">
         <v>0</v>
       </c>
-      <c r="E32" s="29">
+      <c r="E32" s="30">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -4753,18 +4828,18 @@
       <c r="G32" s="7">
         <v>2.5</v>
       </c>
-      <c r="H32" s="25">
+      <c r="H32" s="26">
         <v>3.5</v>
       </c>
-      <c r="I32" s="25">
+      <c r="I32" s="26">
         <f t="shared" si="13"/>
         <v>3.85</v>
       </c>
-      <c r="J32" s="25">
+      <c r="J32" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K32" s="25">
+      <c r="K32" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4775,33 +4850,33 @@
       <c r="N32" s="17">
         <v>10</v>
       </c>
-      <c r="O32" s="33">
+      <c r="O32" s="34">
         <f t="shared" si="4"/>
         <v>34.37</v>
       </c>
-      <c r="Q32" s="34">
+      <c r="Q32" s="35">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="R32" s="34">
+      <c r="R32" s="35">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T32" s="7">
         <v>16</v>
       </c>
-      <c r="U32" s="37">
+      <c r="U32" s="38">
         <f t="shared" si="14"/>
         <v>128</v>
       </c>
-      <c r="V32" s="36"/>
-      <c r="W32" s="36"/>
-      <c r="X32" s="37">
+      <c r="V32" s="37"/>
+      <c r="W32" s="37"/>
+      <c r="X32" s="38">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="Y32" s="36"/>
-      <c r="Z32" s="36"/>
+      <c r="Y32" s="37"/>
+      <c r="Z32" s="37"/>
       <c r="AD32" s="7" t="s">
         <v>152</v>
       </c>
@@ -4831,7 +4906,7 @@
       <c r="D33" s="9">
         <v>0</v>
       </c>
-      <c r="E33" s="29">
+      <c r="E33" s="30">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -4841,18 +4916,18 @@
       <c r="G33" s="7">
         <v>0.4</v>
       </c>
-      <c r="H33" s="25">
+      <c r="H33" s="26">
         <v>2</v>
       </c>
-      <c r="I33" s="25">
+      <c r="I33" s="26">
         <f t="shared" si="13"/>
         <v>1.1</v>
       </c>
-      <c r="J33" s="25">
+      <c r="J33" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K33" s="25">
+      <c r="K33" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4863,33 +4938,33 @@
       <c r="N33" s="17">
         <v>10</v>
       </c>
-      <c r="O33" s="33">
+      <c r="O33" s="34">
         <f t="shared" si="4"/>
         <v>34.37</v>
       </c>
-      <c r="Q33" s="34">
+      <c r="Q33" s="35">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="R33" s="34">
+      <c r="R33" s="35">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T33" s="7">
         <v>16</v>
       </c>
-      <c r="U33" s="37">
+      <c r="U33" s="38">
         <f t="shared" si="14"/>
         <v>48</v>
       </c>
-      <c r="V33" s="36"/>
-      <c r="W33" s="36"/>
-      <c r="X33" s="37">
+      <c r="V33" s="37"/>
+      <c r="W33" s="37"/>
+      <c r="X33" s="38">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="Y33" s="36"/>
-      <c r="Z33" s="36"/>
+      <c r="Y33" s="37"/>
+      <c r="Z33" s="37"/>
       <c r="AD33" s="8" t="s">
         <v>156</v>
       </c>
@@ -4919,7 +4994,7 @@
       <c r="D34" s="9">
         <v>0</v>
       </c>
-      <c r="E34" s="29">
+      <c r="E34" s="30">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -4929,18 +5004,18 @@
       <c r="G34" s="7">
         <v>1.1</v>
       </c>
-      <c r="H34" s="25">
+      <c r="H34" s="26">
         <v>3</v>
       </c>
-      <c r="I34" s="25">
+      <c r="I34" s="26">
         <f t="shared" si="13"/>
         <v>1.5125</v>
       </c>
-      <c r="J34" s="25">
+      <c r="J34" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K34" s="25">
+      <c r="K34" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -4951,33 +5026,33 @@
       <c r="N34" s="17">
         <v>10</v>
       </c>
-      <c r="O34" s="33">
+      <c r="O34" s="34">
         <f t="shared" si="4"/>
         <v>36.57</v>
       </c>
-      <c r="Q34" s="34">
+      <c r="Q34" s="35">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="R34" s="34">
+      <c r="R34" s="35">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T34" s="7">
         <v>32</v>
       </c>
-      <c r="U34" s="37">
+      <c r="U34" s="38">
         <f t="shared" si="14"/>
         <v>64</v>
       </c>
-      <c r="V34" s="36"/>
-      <c r="W34" s="36"/>
-      <c r="X34" s="37">
+      <c r="V34" s="37"/>
+      <c r="W34" s="37"/>
+      <c r="X34" s="38">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="Y34" s="36"/>
-      <c r="Z34" s="36"/>
+      <c r="Y34" s="37"/>
+      <c r="Z34" s="37"/>
       <c r="AD34" s="7" t="s">
         <v>160</v>
       </c>
@@ -5007,7 +5082,7 @@
       <c r="D35" s="9">
         <v>0</v>
       </c>
-      <c r="E35" s="29">
+      <c r="E35" s="30">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5017,18 +5092,18 @@
       <c r="G35" s="7">
         <v>2.2</v>
       </c>
-      <c r="H35" s="25">
+      <c r="H35" s="26">
         <v>4.5</v>
       </c>
-      <c r="I35" s="25">
+      <c r="I35" s="26">
         <f t="shared" si="13"/>
         <v>3.025</v>
       </c>
-      <c r="J35" s="25">
+      <c r="J35" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K35" s="25">
+      <c r="K35" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -5039,33 +5114,33 @@
       <c r="N35" s="17" t="s">
         <v>165</v>
       </c>
-      <c r="O35" s="33">
+      <c r="O35" s="34">
         <f t="shared" si="4"/>
         <v>19</v>
       </c>
-      <c r="Q35" s="34">
+      <c r="Q35" s="35">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="R35" s="34">
+      <c r="R35" s="35">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T35" s="7">
         <v>32</v>
       </c>
-      <c r="U35" s="37">
+      <c r="U35" s="38">
         <f t="shared" si="14"/>
         <v>96</v>
       </c>
-      <c r="V35" s="36"/>
-      <c r="W35" s="36"/>
-      <c r="X35" s="37">
+      <c r="V35" s="37"/>
+      <c r="W35" s="37"/>
+      <c r="X35" s="38">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="Y35" s="36"/>
-      <c r="Z35" s="36"/>
+      <c r="Y35" s="37"/>
+      <c r="Z35" s="37"/>
       <c r="AD35" s="7" t="s">
         <v>166</v>
       </c>
@@ -5095,7 +5170,7 @@
       <c r="D36" s="9">
         <v>0</v>
       </c>
-      <c r="E36" s="29">
+      <c r="E36" s="30">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5105,18 +5180,18 @@
       <c r="G36" s="7">
         <v>0.6</v>
       </c>
-      <c r="H36" s="25">
+      <c r="H36" s="26">
         <v>1</v>
       </c>
-      <c r="I36" s="25">
+      <c r="I36" s="26">
         <f t="shared" si="13"/>
         <v>0.9625</v>
       </c>
-      <c r="J36" s="25">
+      <c r="J36" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K36" s="25">
+      <c r="K36" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -5127,33 +5202,33 @@
       <c r="N36" s="17">
         <v>10</v>
       </c>
-      <c r="O36" s="33">
+      <c r="O36" s="34">
         <f t="shared" si="4"/>
         <v>34.37</v>
       </c>
-      <c r="Q36" s="34">
+      <c r="Q36" s="35">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="R36" s="34">
+      <c r="R36" s="35">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T36" s="7">
         <v>16</v>
       </c>
-      <c r="U36" s="37">
+      <c r="U36" s="38">
         <f t="shared" si="14"/>
         <v>32</v>
       </c>
-      <c r="V36" s="36"/>
-      <c r="W36" s="36"/>
-      <c r="X36" s="37">
+      <c r="V36" s="37"/>
+      <c r="W36" s="37"/>
+      <c r="X36" s="38">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="Y36" s="36"/>
-      <c r="Z36" s="36"/>
+      <c r="Y36" s="37"/>
+      <c r="Z36" s="37"/>
       <c r="AD36" s="7" t="s">
         <v>170</v>
       </c>
@@ -5183,7 +5258,7 @@
       <c r="D37" s="9">
         <v>0</v>
       </c>
-      <c r="E37" s="29">
+      <c r="E37" s="30">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5193,18 +5268,18 @@
       <c r="G37" s="7">
         <v>0.5</v>
       </c>
-      <c r="H37" s="25">
+      <c r="H37" s="26">
         <v>1</v>
       </c>
-      <c r="I37" s="25">
+      <c r="I37" s="26">
         <f t="shared" si="13"/>
         <v>0.6875</v>
       </c>
-      <c r="J37" s="25">
+      <c r="J37" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K37" s="25">
+      <c r="K37" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -5215,33 +5290,33 @@
       <c r="N37" s="17">
         <v>10</v>
       </c>
-      <c r="O37" s="33">
+      <c r="O37" s="34">
         <f t="shared" si="4"/>
         <v>34.37</v>
       </c>
-      <c r="Q37" s="34">
+      <c r="Q37" s="35">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="R37" s="34">
+      <c r="R37" s="35">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T37" s="7">
         <v>16</v>
       </c>
-      <c r="U37" s="37">
+      <c r="U37" s="38">
         <f t="shared" si="14"/>
         <v>32</v>
       </c>
-      <c r="V37" s="36"/>
-      <c r="W37" s="36"/>
-      <c r="X37" s="37">
+      <c r="V37" s="37"/>
+      <c r="W37" s="37"/>
+      <c r="X37" s="38">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="Y37" s="36"/>
-      <c r="Z37" s="36"/>
+      <c r="Y37" s="37"/>
+      <c r="Z37" s="37"/>
       <c r="AD37" s="8" t="s">
         <v>174</v>
       </c>
@@ -5271,7 +5346,7 @@
       <c r="D38" s="9">
         <v>0</v>
       </c>
-      <c r="E38" s="26">
+      <c r="E38" s="27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5281,18 +5356,18 @@
       <c r="G38" s="7">
         <v>1</v>
       </c>
-      <c r="H38" s="25">
+      <c r="H38" s="26">
         <v>3.5</v>
       </c>
-      <c r="I38" s="25">
+      <c r="I38" s="26">
         <f t="shared" si="13"/>
         <v>3.4375</v>
       </c>
-      <c r="J38" s="25">
+      <c r="J38" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K38" s="25">
+      <c r="K38" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -5303,33 +5378,33 @@
       <c r="N38" s="17">
         <v>10</v>
       </c>
-      <c r="O38" s="33">
+      <c r="O38" s="34">
         <f t="shared" si="4"/>
         <v>34.37</v>
       </c>
-      <c r="Q38" s="34">
+      <c r="Q38" s="35">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="R38" s="34">
+      <c r="R38" s="35">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T38" s="7">
         <v>16</v>
       </c>
-      <c r="U38" s="37">
+      <c r="U38" s="38">
         <f t="shared" si="14"/>
         <v>112</v>
       </c>
-      <c r="V38" s="36"/>
-      <c r="W38" s="36"/>
-      <c r="X38" s="37">
+      <c r="V38" s="37"/>
+      <c r="W38" s="37"/>
+      <c r="X38" s="38">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="Y38" s="36"/>
-      <c r="Z38" s="36"/>
+      <c r="Y38" s="37"/>
+      <c r="Z38" s="37"/>
       <c r="AD38" s="7" t="s">
         <v>178</v>
       </c>
@@ -5359,7 +5434,7 @@
       <c r="D39" s="9">
         <v>0</v>
       </c>
-      <c r="E39" s="26">
+      <c r="E39" s="27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5369,19 +5444,19 @@
       <c r="G39" s="7">
         <v>0.3</v>
       </c>
-      <c r="H39" s="25">
+      <c r="H39" s="26">
         <f t="shared" ref="H39:H51" si="16">MAX(E39,F39)*1.375</f>
         <v>0.55</v>
       </c>
-      <c r="I39" s="25">
+      <c r="I39" s="26">
         <f t="shared" si="13"/>
         <v>0.55</v>
       </c>
-      <c r="J39" s="25">
+      <c r="J39" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K39" s="25">
+      <c r="K39" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -5392,33 +5467,33 @@
       <c r="N39" s="17" t="s">
         <v>183</v>
       </c>
-      <c r="O39" s="33">
+      <c r="O39" s="34">
         <f t="shared" si="4"/>
         <v>30.8</v>
       </c>
-      <c r="Q39" s="34">
+      <c r="Q39" s="35">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="R39" s="34">
+      <c r="R39" s="35">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T39" s="7">
         <v>20</v>
       </c>
-      <c r="U39" s="37">
+      <c r="U39" s="38">
         <f t="shared" si="14"/>
         <v>20</v>
       </c>
-      <c r="V39" s="36"/>
-      <c r="W39" s="36"/>
-      <c r="X39" s="37">
+      <c r="V39" s="37"/>
+      <c r="W39" s="37"/>
+      <c r="X39" s="38">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="Y39" s="36"/>
-      <c r="Z39" s="36"/>
+      <c r="Y39" s="37"/>
+      <c r="Z39" s="37"/>
       <c r="AD39" s="7" t="s">
         <v>184</v>
       </c>
@@ -5448,7 +5523,7 @@
       <c r="D40" s="9">
         <v>0</v>
       </c>
-      <c r="E40" s="26">
+      <c r="E40" s="27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5458,19 +5533,19 @@
       <c r="G40" s="7">
         <v>0.1</v>
       </c>
-      <c r="H40" s="25">
+      <c r="H40" s="26">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="I40" s="25">
+      <c r="I40" s="26">
         <f t="shared" si="13"/>
         <v>0.1375</v>
       </c>
-      <c r="J40" s="25">
+      <c r="J40" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K40" s="25">
+      <c r="K40" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -5481,33 +5556,33 @@
       <c r="N40" s="17" t="s">
         <v>183</v>
       </c>
-      <c r="O40" s="33">
+      <c r="O40" s="34">
         <f t="shared" si="4"/>
         <v>32.8</v>
       </c>
-      <c r="Q40" s="34">
+      <c r="Q40" s="35">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="R40" s="34">
+      <c r="R40" s="35">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T40" s="7">
         <v>20</v>
       </c>
-      <c r="U40" s="37">
+      <c r="U40" s="38">
         <f t="shared" si="14"/>
         <v>20</v>
       </c>
-      <c r="V40" s="36"/>
-      <c r="W40" s="36"/>
-      <c r="X40" s="37">
+      <c r="V40" s="37"/>
+      <c r="W40" s="37"/>
+      <c r="X40" s="38">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="Y40" s="36"/>
-      <c r="Z40" s="36"/>
+      <c r="Y40" s="37"/>
+      <c r="Z40" s="37"/>
       <c r="AD40" s="7" t="s">
         <v>188</v>
       </c>
@@ -5537,7 +5612,7 @@
       <c r="D41" s="9">
         <v>0</v>
       </c>
-      <c r="E41" s="26">
+      <c r="E41" s="27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5547,18 +5622,18 @@
       <c r="G41" s="7">
         <v>0</v>
       </c>
-      <c r="H41" s="25">
+      <c r="H41" s="26">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="I41" s="25">
+      <c r="I41" s="26">
         <v>1</v>
       </c>
-      <c r="J41" s="25">
+      <c r="J41" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K41" s="25">
+      <c r="K41" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -5568,33 +5643,33 @@
       <c r="N41" s="17">
         <v>10</v>
       </c>
-      <c r="O41" s="33">
+      <c r="O41" s="34">
         <f t="shared" si="4"/>
         <v>36.57</v>
       </c>
-      <c r="Q41" s="34">
+      <c r="Q41" s="35">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="R41" s="34">
+      <c r="R41" s="35">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T41" s="7">
         <v>16</v>
       </c>
-      <c r="U41" s="37">
+      <c r="U41" s="38">
         <f t="shared" si="14"/>
         <v>32</v>
       </c>
-      <c r="V41" s="36"/>
-      <c r="W41" s="36"/>
-      <c r="X41" s="37">
+      <c r="V41" s="37"/>
+      <c r="W41" s="37"/>
+      <c r="X41" s="38">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="Y41" s="36"/>
-      <c r="Z41" s="36"/>
+      <c r="Y41" s="37"/>
+      <c r="Z41" s="37"/>
       <c r="AD41" s="7" t="s">
         <v>192</v>
       </c>
@@ -5624,7 +5699,7 @@
       <c r="D42" s="9">
         <v>0</v>
       </c>
-      <c r="E42" s="26">
+      <c r="E42" s="27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5634,18 +5709,18 @@
       <c r="G42" s="7">
         <v>0</v>
       </c>
-      <c r="H42" s="25">
+      <c r="H42" s="26">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="I42" s="25">
+      <c r="I42" s="26">
         <v>1</v>
       </c>
-      <c r="J42" s="25">
+      <c r="J42" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K42" s="25">
+      <c r="K42" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -5655,33 +5730,33 @@
       <c r="N42" s="17">
         <v>10</v>
       </c>
-      <c r="O42" s="33">
+      <c r="O42" s="34">
         <f t="shared" si="4"/>
         <v>36.57</v>
       </c>
-      <c r="Q42" s="34">
+      <c r="Q42" s="35">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="R42" s="34">
+      <c r="R42" s="35">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T42" s="7">
         <v>16</v>
       </c>
-      <c r="U42" s="37">
+      <c r="U42" s="38">
         <f t="shared" si="14"/>
         <v>32</v>
       </c>
-      <c r="V42" s="36"/>
-      <c r="W42" s="36"/>
-      <c r="X42" s="37">
+      <c r="V42" s="37"/>
+      <c r="W42" s="37"/>
+      <c r="X42" s="38">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="Y42" s="36"/>
-      <c r="Z42" s="36"/>
+      <c r="Y42" s="37"/>
+      <c r="Z42" s="37"/>
       <c r="AD42" s="7" t="s">
         <v>196</v>
       </c>
@@ -5711,7 +5786,7 @@
       <c r="D43" s="9">
         <v>0</v>
       </c>
-      <c r="E43" s="26">
+      <c r="E43" s="27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5721,18 +5796,18 @@
       <c r="G43" s="7">
         <v>0</v>
       </c>
-      <c r="H43" s="25">
+      <c r="H43" s="26">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="I43" s="25">
+      <c r="I43" s="26">
         <v>1</v>
       </c>
-      <c r="J43" s="25">
+      <c r="J43" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K43" s="25">
+      <c r="K43" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -5742,33 +5817,33 @@
       <c r="N43" s="7">
         <v>5</v>
       </c>
-      <c r="O43" s="33">
+      <c r="O43" s="34">
         <f t="shared" si="4"/>
         <v>18.3</v>
       </c>
-      <c r="Q43" s="34">
+      <c r="Q43" s="35">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="R43" s="34">
+      <c r="R43" s="35">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T43" s="7">
         <v>32</v>
       </c>
-      <c r="U43" s="37">
+      <c r="U43" s="38">
         <f t="shared" si="14"/>
         <v>32</v>
       </c>
-      <c r="V43" s="36"/>
-      <c r="W43" s="36"/>
-      <c r="X43" s="37">
+      <c r="V43" s="37"/>
+      <c r="W43" s="37"/>
+      <c r="X43" s="38">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="Y43" s="36"/>
-      <c r="Z43" s="36"/>
+      <c r="Y43" s="37"/>
+      <c r="Z43" s="37"/>
       <c r="AD43" s="7" t="s">
         <v>200</v>
       </c>
@@ -5798,7 +5873,7 @@
       <c r="D44" s="9">
         <v>0</v>
       </c>
-      <c r="E44" s="26">
+      <c r="E44" s="27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5808,18 +5883,18 @@
       <c r="G44" s="7">
         <v>0</v>
       </c>
-      <c r="H44" s="25">
+      <c r="H44" s="26">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="I44" s="25">
+      <c r="I44" s="26">
         <v>1</v>
       </c>
-      <c r="J44" s="25">
+      <c r="J44" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K44" s="25">
+      <c r="K44" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -5829,33 +5904,33 @@
       <c r="N44" s="7">
         <v>3</v>
       </c>
-      <c r="O44" s="33">
+      <c r="O44" s="34">
         <f t="shared" si="4"/>
         <v>13</v>
       </c>
-      <c r="Q44" s="34">
+      <c r="Q44" s="35">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="R44" s="34">
+      <c r="R44" s="35">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="T44" s="7">
         <v>72</v>
       </c>
-      <c r="U44" s="37">
+      <c r="U44" s="38">
         <f t="shared" si="14"/>
         <v>72</v>
       </c>
-      <c r="V44" s="36"/>
-      <c r="W44" s="36"/>
-      <c r="X44" s="37">
+      <c r="V44" s="37"/>
+      <c r="W44" s="37"/>
+      <c r="X44" s="38">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="Y44" s="36"/>
-      <c r="Z44" s="36"/>
+      <c r="Y44" s="37"/>
+      <c r="Z44" s="37"/>
       <c r="AD44" s="7" t="s">
         <v>204</v>
       </c>
@@ -5885,7 +5960,7 @@
       <c r="D45" s="9">
         <v>0</v>
       </c>
-      <c r="E45" s="26">
+      <c r="E45" s="27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5895,18 +5970,18 @@
       <c r="G45" s="7">
         <v>0</v>
       </c>
-      <c r="H45" s="25">
+      <c r="H45" s="26">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="I45" s="25">
+      <c r="I45" s="26">
         <v>1</v>
       </c>
-      <c r="J45" s="25">
+      <c r="J45" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K45" s="25">
+      <c r="K45" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -5916,33 +5991,33 @@
       <c r="N45" s="7">
         <v>12</v>
       </c>
-      <c r="O45" s="33">
+      <c r="O45" s="34">
         <f t="shared" si="4"/>
         <v>51</v>
       </c>
-      <c r="Q45" s="34">
-        <f t="shared" ref="Q45:Q53" si="17">M45*C45</f>
-        <v>0</v>
-      </c>
-      <c r="R45" s="34">
-        <f t="shared" ref="R45:R53" si="18">M45*D45</f>
+      <c r="Q45" s="35">
+        <f t="shared" ref="Q45:Q60" si="17">M45*C45</f>
+        <v>0</v>
+      </c>
+      <c r="R45" s="35">
+        <f t="shared" ref="R45:R60" si="18">M45*D45</f>
         <v>0</v>
       </c>
       <c r="T45" s="7">
         <v>18</v>
       </c>
-      <c r="U45" s="37">
-        <f t="shared" ref="U45:U53" si="19">CEILING(MAX(0,90-MAX(K45,60))*I45/T45,1)*T45</f>
+      <c r="U45" s="38">
+        <f t="shared" ref="U45:U55" si="19">CEILING(MAX(0,90-MAX(K45,60))*I45/T45,1)*T45</f>
         <v>36</v>
       </c>
-      <c r="V45" s="36"/>
-      <c r="W45" s="36"/>
-      <c r="X45" s="37">
-        <f t="shared" ref="X45:X53" si="20">MIN(CEILING(MAX(0,70-MAX(J45,30))*I45/T45,1)*T45,D45)</f>
-        <v>0</v>
-      </c>
-      <c r="Y45" s="36"/>
-      <c r="Z45" s="36"/>
+      <c r="V45" s="37"/>
+      <c r="W45" s="37"/>
+      <c r="X45" s="38">
+        <f t="shared" ref="X45:X55" si="20">MIN(CEILING(MAX(0,70-MAX(J45,30))*I45/T45,1)*T45,D45)</f>
+        <v>0</v>
+      </c>
+      <c r="Y45" s="37"/>
+      <c r="Z45" s="37"/>
       <c r="AD45" s="7" t="s">
         <v>208</v>
       </c>
@@ -5972,7 +6047,7 @@
       <c r="D46" s="9">
         <v>0</v>
       </c>
-      <c r="E46" s="26">
+      <c r="E46" s="27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -5982,18 +6057,18 @@
       <c r="G46" s="7">
         <v>0</v>
       </c>
-      <c r="H46" s="25">
+      <c r="H46" s="26">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="I46" s="25">
+      <c r="I46" s="26">
         <v>1</v>
       </c>
-      <c r="J46" s="25">
+      <c r="J46" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K46" s="25">
+      <c r="K46" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -6003,33 +6078,33 @@
       <c r="N46" s="17">
         <v>6</v>
       </c>
-      <c r="O46" s="33">
-        <f t="shared" ref="O46:O53" si="21">M46+N46</f>
+      <c r="O46" s="34">
+        <f t="shared" ref="O46:O60" si="21">M46+N46</f>
         <v>25.5</v>
       </c>
-      <c r="Q46" s="34">
+      <c r="Q46" s="35">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="R46" s="34">
+      <c r="R46" s="35">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="T46" s="7">
         <v>20</v>
       </c>
-      <c r="U46" s="37">
+      <c r="U46" s="38">
         <f t="shared" si="19"/>
         <v>40</v>
       </c>
-      <c r="V46" s="36"/>
-      <c r="W46" s="36"/>
-      <c r="X46" s="37">
+      <c r="V46" s="37"/>
+      <c r="W46" s="37"/>
+      <c r="X46" s="38">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="Y46" s="36"/>
-      <c r="Z46" s="36"/>
+      <c r="Y46" s="37"/>
+      <c r="Z46" s="37"/>
       <c r="AD46" s="7" t="s">
         <v>212</v>
       </c>
@@ -6059,7 +6134,7 @@
       <c r="D47" s="9">
         <v>0</v>
       </c>
-      <c r="E47" s="26">
+      <c r="E47" s="27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -6069,18 +6144,18 @@
       <c r="G47" s="7">
         <v>0</v>
       </c>
-      <c r="H47" s="25">
+      <c r="H47" s="26">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="I47" s="25">
+      <c r="I47" s="26">
         <v>1</v>
       </c>
-      <c r="J47" s="25">
+      <c r="J47" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K47" s="25">
+      <c r="K47" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -6090,33 +6165,33 @@
       <c r="N47" s="17">
         <v>6</v>
       </c>
-      <c r="O47" s="33">
+      <c r="O47" s="34">
         <f t="shared" si="21"/>
         <v>25.5</v>
       </c>
-      <c r="Q47" s="34">
+      <c r="Q47" s="35">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="R47" s="34">
+      <c r="R47" s="35">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="T47" s="7">
         <v>20</v>
       </c>
-      <c r="U47" s="37">
+      <c r="U47" s="38">
         <f t="shared" si="19"/>
         <v>40</v>
       </c>
-      <c r="V47" s="36"/>
-      <c r="W47" s="36"/>
-      <c r="X47" s="37">
+      <c r="V47" s="37"/>
+      <c r="W47" s="37"/>
+      <c r="X47" s="38">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="Y47" s="36"/>
-      <c r="Z47" s="36"/>
+      <c r="Y47" s="37"/>
+      <c r="Z47" s="37"/>
       <c r="AD47" s="7" t="s">
         <v>216</v>
       </c>
@@ -6146,7 +6221,7 @@
       <c r="D48" s="9">
         <v>0</v>
       </c>
-      <c r="E48" s="26">
+      <c r="E48" s="27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -6156,18 +6231,18 @@
       <c r="G48" s="7">
         <v>0</v>
       </c>
-      <c r="H48" s="25">
+      <c r="H48" s="26">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="I48" s="25">
+      <c r="I48" s="26">
         <v>1</v>
       </c>
-      <c r="J48" s="25">
+      <c r="J48" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K48" s="25">
+      <c r="K48" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -6177,33 +6252,33 @@
       <c r="N48" s="17">
         <v>6</v>
       </c>
-      <c r="O48" s="33">
+      <c r="O48" s="34">
         <f t="shared" si="21"/>
         <v>25.5</v>
       </c>
-      <c r="Q48" s="34">
+      <c r="Q48" s="35">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="R48" s="34">
+      <c r="R48" s="35">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="T48" s="7">
         <v>20</v>
       </c>
-      <c r="U48" s="37">
+      <c r="U48" s="38">
         <f t="shared" si="19"/>
         <v>40</v>
       </c>
-      <c r="V48" s="36"/>
-      <c r="W48" s="36"/>
-      <c r="X48" s="37">
+      <c r="V48" s="37"/>
+      <c r="W48" s="37"/>
+      <c r="X48" s="38">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="Y48" s="36"/>
-      <c r="Z48" s="36"/>
+      <c r="Y48" s="37"/>
+      <c r="Z48" s="37"/>
       <c r="AD48" s="7" t="s">
         <v>220</v>
       </c>
@@ -6233,7 +6308,7 @@
       <c r="D49" s="9">
         <v>0</v>
       </c>
-      <c r="E49" s="26">
+      <c r="E49" s="27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -6243,18 +6318,18 @@
       <c r="G49" s="7">
         <v>0</v>
       </c>
-      <c r="H49" s="25">
+      <c r="H49" s="26">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="I49" s="25">
+      <c r="I49" s="26">
         <v>1</v>
       </c>
-      <c r="J49" s="25">
+      <c r="J49" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K49" s="25">
+      <c r="K49" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -6264,33 +6339,33 @@
       <c r="N49" s="17">
         <v>10</v>
       </c>
-      <c r="O49" s="33">
+      <c r="O49" s="34">
         <f t="shared" si="21"/>
         <v>34.37</v>
       </c>
-      <c r="Q49" s="34">
+      <c r="Q49" s="35">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="R49" s="34">
+      <c r="R49" s="35">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="T49" s="7">
         <v>16</v>
       </c>
-      <c r="U49" s="37">
+      <c r="U49" s="38">
         <f t="shared" si="19"/>
         <v>32</v>
       </c>
-      <c r="V49" s="36"/>
-      <c r="W49" s="36"/>
-      <c r="X49" s="37">
+      <c r="V49" s="37"/>
+      <c r="W49" s="37"/>
+      <c r="X49" s="38">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="Y49" s="36"/>
-      <c r="Z49" s="36"/>
+      <c r="Y49" s="37"/>
+      <c r="Z49" s="37"/>
       <c r="AD49" s="7" t="s">
         <v>224</v>
       </c>
@@ -6320,7 +6395,7 @@
       <c r="D50" s="9">
         <v>0</v>
       </c>
-      <c r="E50" s="26">
+      <c r="E50" s="27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -6330,18 +6405,18 @@
       <c r="G50" s="7">
         <v>0</v>
       </c>
-      <c r="H50" s="25">
+      <c r="H50" s="26">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="I50" s="25">
+      <c r="I50" s="26">
         <v>1</v>
       </c>
-      <c r="J50" s="25">
+      <c r="J50" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K50" s="25">
+      <c r="K50" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -6351,33 +6426,33 @@
       <c r="N50" s="17">
         <v>10</v>
       </c>
-      <c r="O50" s="33">
+      <c r="O50" s="34">
         <f t="shared" si="21"/>
         <v>34.37</v>
       </c>
-      <c r="Q50" s="34">
+      <c r="Q50" s="35">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="R50" s="34">
+      <c r="R50" s="35">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="T50" s="7">
         <v>16</v>
       </c>
-      <c r="U50" s="37">
+      <c r="U50" s="38">
         <f t="shared" si="19"/>
         <v>32</v>
       </c>
-      <c r="V50" s="36"/>
-      <c r="W50" s="36"/>
-      <c r="X50" s="37">
+      <c r="V50" s="37"/>
+      <c r="W50" s="37"/>
+      <c r="X50" s="38">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="Y50" s="36"/>
-      <c r="Z50" s="36"/>
+      <c r="Y50" s="37"/>
+      <c r="Z50" s="37"/>
       <c r="AD50" s="7" t="s">
         <v>228</v>
       </c>
@@ -6407,7 +6482,7 @@
       <c r="D51" s="9">
         <v>0</v>
       </c>
-      <c r="E51" s="26">
+      <c r="E51" s="27">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -6417,18 +6492,18 @@
       <c r="G51" s="7">
         <v>0</v>
       </c>
-      <c r="H51" s="25">
+      <c r="H51" s="26">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="I51" s="25">
+      <c r="I51" s="26">
         <v>1</v>
       </c>
-      <c r="J51" s="25">
+      <c r="J51" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K51" s="25">
+      <c r="K51" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -6438,33 +6513,33 @@
       <c r="N51" s="7">
         <v>5</v>
       </c>
-      <c r="O51" s="33">
+      <c r="O51" s="34">
         <f t="shared" si="21"/>
         <v>18.3</v>
       </c>
-      <c r="Q51" s="34">
+      <c r="Q51" s="35">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="R51" s="34">
+      <c r="R51" s="35">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="T51" s="7">
         <v>32</v>
       </c>
-      <c r="U51" s="37">
+      <c r="U51" s="38">
         <f t="shared" si="19"/>
         <v>32</v>
       </c>
-      <c r="V51" s="36"/>
-      <c r="W51" s="36"/>
-      <c r="X51" s="37">
+      <c r="V51" s="37"/>
+      <c r="W51" s="37"/>
+      <c r="X51" s="38">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="Y51" s="36"/>
-      <c r="Z51" s="36"/>
+      <c r="Y51" s="37"/>
+      <c r="Z51" s="37"/>
       <c r="AD51" s="7" t="s">
         <v>232</v>
       </c>
@@ -6494,7 +6569,7 @@
       <c r="D52" s="9">
         <v>0</v>
       </c>
-      <c r="E52" s="29">
+      <c r="E52" s="30">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -6504,18 +6579,18 @@
       <c r="G52" s="7">
         <v>0.5</v>
       </c>
-      <c r="H52" s="25">
+      <c r="H52" s="26">
         <v>1</v>
       </c>
-      <c r="I52" s="25">
-        <f>MAX(F52,G52)*1.375</f>
+      <c r="I52" s="26">
+        <f t="shared" ref="I52:I60" si="22">MAX(F52,G52)*1.375</f>
         <v>0.6875</v>
       </c>
-      <c r="J52" s="25">
+      <c r="J52" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K52" s="25">
+      <c r="K52" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -6526,33 +6601,33 @@
       <c r="N52" s="17">
         <v>10</v>
       </c>
-      <c r="O52" s="33">
+      <c r="O52" s="34">
         <f t="shared" si="21"/>
         <v>34.37</v>
       </c>
-      <c r="Q52" s="34">
+      <c r="Q52" s="35">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="R52" s="34">
+      <c r="R52" s="35">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="T52" s="7">
         <v>16</v>
       </c>
-      <c r="U52" s="37">
+      <c r="U52" s="38">
         <f t="shared" si="19"/>
         <v>32</v>
       </c>
-      <c r="V52" s="36"/>
-      <c r="W52" s="36"/>
-      <c r="X52" s="37">
+      <c r="V52" s="37"/>
+      <c r="W52" s="37"/>
+      <c r="X52" s="38">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="Y52" s="36"/>
-      <c r="Z52" s="36"/>
+      <c r="Y52" s="37"/>
+      <c r="Z52" s="37"/>
       <c r="AD52" s="1" t="s">
         <v>235</v>
       </c>
@@ -6582,7 +6657,7 @@
       <c r="D53" s="9">
         <v>0</v>
       </c>
-      <c r="E53" s="29">
+      <c r="E53" s="30">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
@@ -6592,18 +6667,18 @@
       <c r="G53" s="7">
         <v>0.5</v>
       </c>
-      <c r="H53" s="25">
+      <c r="H53" s="26">
         <v>1</v>
       </c>
-      <c r="I53" s="25">
-        <f>MAX(F53,G53)*1.375</f>
+      <c r="I53" s="26">
+        <f t="shared" si="22"/>
         <v>0.6875</v>
       </c>
-      <c r="J53" s="25">
+      <c r="J53" s="26">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="K53" s="25">
+      <c r="K53" s="26">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
@@ -6614,33 +6689,33 @@
       <c r="N53" s="17">
         <v>10</v>
       </c>
-      <c r="O53" s="33">
+      <c r="O53" s="34">
         <f t="shared" si="21"/>
         <v>34.37</v>
       </c>
-      <c r="Q53" s="34">
+      <c r="Q53" s="35">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="R53" s="34">
+      <c r="R53" s="35">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="T53" s="7">
         <v>16</v>
       </c>
-      <c r="U53" s="37">
+      <c r="U53" s="38">
         <f t="shared" si="19"/>
         <v>32</v>
       </c>
-      <c r="V53" s="36"/>
-      <c r="W53" s="36"/>
-      <c r="X53" s="37">
+      <c r="V53" s="37"/>
+      <c r="W53" s="37"/>
+      <c r="X53" s="38">
         <f t="shared" si="20"/>
         <v>0</v>
       </c>
-      <c r="Y53" s="36"/>
-      <c r="Z53" s="36"/>
+      <c r="Y53" s="37"/>
+      <c r="Z53" s="37"/>
       <c r="AD53" s="1" t="s">
         <v>239</v>
       </c>
@@ -6670,28 +6745,28 @@
       <c r="D54" s="9">
         <v>0</v>
       </c>
-      <c r="E54" s="26">
-        <f>C54+D54</f>
-        <v>0</v>
-      </c>
-      <c r="F54" s="27">
-        <v>0</v>
-      </c>
-      <c r="G54" s="28">
-        <v>0</v>
-      </c>
-      <c r="H54" s="25">
-        <v>0</v>
-      </c>
-      <c r="I54" s="25">
+      <c r="E54" s="27">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F54" s="28">
+        <v>0</v>
+      </c>
+      <c r="G54" s="29">
+        <v>0</v>
+      </c>
+      <c r="H54" s="26">
+        <v>0</v>
+      </c>
+      <c r="I54" s="26">
         <v>1</v>
       </c>
-      <c r="J54" s="25">
-        <f>(C54)/I54</f>
-        <v>0</v>
-      </c>
-      <c r="K54" s="25">
-        <f>(E54)/I54</f>
+      <c r="J54" s="26">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K54" s="26">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="L54" s="17"/>
@@ -6701,33 +6776,33 @@
       <c r="N54" s="17">
         <v>10</v>
       </c>
-      <c r="O54" s="33">
-        <f>M54+N54</f>
+      <c r="O54" s="34">
+        <f t="shared" si="21"/>
         <v>34.37</v>
       </c>
-      <c r="Q54" s="34">
-        <f>M54*C54</f>
-        <v>0</v>
-      </c>
-      <c r="R54" s="34">
-        <f>M54*D54</f>
+      <c r="Q54" s="35">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="R54" s="35">
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="T54" s="7">
         <v>16</v>
       </c>
-      <c r="U54" s="37">
-        <f>CEILING(MAX(0,90-MAX(K54,60))*I54/T54,1)*T54</f>
+      <c r="U54" s="38">
+        <f t="shared" si="19"/>
         <v>32</v>
       </c>
-      <c r="V54" s="36"/>
-      <c r="W54" s="36"/>
-      <c r="X54" s="37">
-        <f>MIN(CEILING(MAX(0,70-MAX(J54,30))*I54/T54,1)*T54,D54)</f>
-        <v>0</v>
-      </c>
-      <c r="Y54" s="36"/>
-      <c r="Z54" s="36"/>
+      <c r="V54" s="37"/>
+      <c r="W54" s="37"/>
+      <c r="X54" s="38">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="Y54" s="37"/>
+      <c r="Z54" s="37"/>
       <c r="AD54" s="1" t="s">
         <v>242</v>
       </c>
@@ -6744,12 +6819,534 @@
         <v>45</v>
       </c>
     </row>
-    <row r="55" ht="25" customHeight="1"/>
-    <row r="56" ht="25" customHeight="1"/>
-    <row r="57" ht="25" customHeight="1"/>
-    <row r="58" ht="25" customHeight="1"/>
-    <row r="59" ht="25" customHeight="1"/>
-    <row r="60" ht="25" customHeight="1"/>
+    <row r="55" ht="25" customHeight="1" spans="1:34">
+      <c r="A55" s="24" t="s">
+        <v>244</v>
+      </c>
+      <c r="B55" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="C55" s="9">
+        <v>0</v>
+      </c>
+      <c r="D55" s="9">
+        <v>0</v>
+      </c>
+      <c r="E55" s="27">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F55" s="28">
+        <v>1</v>
+      </c>
+      <c r="G55" s="29">
+        <v>1</v>
+      </c>
+      <c r="H55" s="26">
+        <v>1</v>
+      </c>
+      <c r="I55" s="26">
+        <f t="shared" si="22"/>
+        <v>1.375</v>
+      </c>
+      <c r="J55" s="26">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K55" s="26">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L55" s="17"/>
+      <c r="M55" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="N55" s="17" t="s">
+        <v>165</v>
+      </c>
+      <c r="O55" s="34">
+        <f t="shared" si="21"/>
+        <v>19</v>
+      </c>
+      <c r="Q55" s="35">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="R55" s="35">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="T55" s="7">
+        <v>32</v>
+      </c>
+      <c r="U55" s="38">
+        <f t="shared" si="19"/>
+        <v>64</v>
+      </c>
+      <c r="V55" s="37"/>
+      <c r="W55" s="37"/>
+      <c r="X55" s="38">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="Y55" s="37"/>
+      <c r="Z55" s="37"/>
+      <c r="AD55" s="7" t="s">
+        <v>246</v>
+      </c>
+      <c r="AE55" s="7" t="s">
+        <v>247</v>
+      </c>
+      <c r="AF55" s="7">
+        <v>30</v>
+      </c>
+      <c r="AG55" s="7">
+        <v>40</v>
+      </c>
+      <c r="AH55" s="7">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="56" ht="25" customHeight="1" spans="1:34">
+      <c r="A56" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="B56" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="C56" s="9">
+        <v>0</v>
+      </c>
+      <c r="D56" s="9">
+        <v>0</v>
+      </c>
+      <c r="E56" s="27">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F56" s="28">
+        <v>1</v>
+      </c>
+      <c r="G56" s="29">
+        <v>1</v>
+      </c>
+      <c r="H56" s="26">
+        <v>1</v>
+      </c>
+      <c r="I56" s="26">
+        <f t="shared" si="22"/>
+        <v>1.375</v>
+      </c>
+      <c r="J56" s="26">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K56" s="26">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L56" s="17"/>
+      <c r="M56" s="17">
+        <v>26.57</v>
+      </c>
+      <c r="N56" s="17">
+        <v>10</v>
+      </c>
+      <c r="O56" s="34">
+        <f t="shared" si="21"/>
+        <v>36.57</v>
+      </c>
+      <c r="Q56" s="35">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="R56" s="35">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="T56" s="7">
+        <v>32</v>
+      </c>
+      <c r="U56" s="37"/>
+      <c r="V56" s="37"/>
+      <c r="W56" s="38">
+        <f>CEILING(MAX(0,135-MAX(K56,60))*I56/T56,1)*T56</f>
+        <v>128</v>
+      </c>
+      <c r="X56" s="37"/>
+      <c r="Y56" s="37"/>
+      <c r="Z56" s="38">
+        <f>MIN(CEILING(MAX(0,115-MAX(J56,30))*I56/T56,1)*T56,D56)</f>
+        <v>0</v>
+      </c>
+      <c r="AD56" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="AE56" s="7" t="s">
+        <v>251</v>
+      </c>
+      <c r="AF56" s="7">
+        <v>60</v>
+      </c>
+      <c r="AG56" s="7">
+        <v>40</v>
+      </c>
+      <c r="AH56" s="7">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="57" ht="25" customHeight="1" spans="1:34">
+      <c r="A57" s="24" t="s">
+        <v>252</v>
+      </c>
+      <c r="B57" s="11" t="s">
+        <v>253</v>
+      </c>
+      <c r="C57" s="9">
+        <v>0</v>
+      </c>
+      <c r="D57" s="9">
+        <v>0</v>
+      </c>
+      <c r="E57" s="27">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F57" s="28">
+        <v>1</v>
+      </c>
+      <c r="G57" s="29">
+        <v>1</v>
+      </c>
+      <c r="H57" s="26">
+        <v>1</v>
+      </c>
+      <c r="I57" s="26">
+        <f t="shared" si="22"/>
+        <v>1.375</v>
+      </c>
+      <c r="J57" s="26">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K57" s="26">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L57" s="17"/>
+      <c r="M57" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="N57" s="17" t="s">
+        <v>165</v>
+      </c>
+      <c r="O57" s="34">
+        <f t="shared" si="21"/>
+        <v>19</v>
+      </c>
+      <c r="Q57" s="35">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="R57" s="35">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="T57" s="7">
+        <v>32</v>
+      </c>
+      <c r="U57" s="38">
+        <f t="shared" ref="U57:U60" si="23">CEILING(MAX(0,90-MAX(K57,60))*I57/T57,1)*T57</f>
+        <v>64</v>
+      </c>
+      <c r="V57" s="37"/>
+      <c r="W57" s="37"/>
+      <c r="X57" s="38">
+        <f t="shared" ref="X57:X60" si="24">MIN(CEILING(MAX(0,70-MAX(J57,30))*I57/T57,1)*T57,D57)</f>
+        <v>0</v>
+      </c>
+      <c r="Y57" s="37"/>
+      <c r="Z57" s="37"/>
+      <c r="AD57" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="AE57" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="AF57" s="7">
+        <v>30</v>
+      </c>
+      <c r="AG57" s="7">
+        <v>40</v>
+      </c>
+      <c r="AH57" s="7">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="58" ht="25" customHeight="1" spans="1:34">
+      <c r="A58" s="24" t="s">
+        <v>256</v>
+      </c>
+      <c r="B58" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="C58" s="9">
+        <v>0</v>
+      </c>
+      <c r="D58" s="9">
+        <v>0</v>
+      </c>
+      <c r="E58" s="27">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F58" s="28">
+        <v>1</v>
+      </c>
+      <c r="G58" s="29">
+        <v>1</v>
+      </c>
+      <c r="H58" s="26">
+        <v>1</v>
+      </c>
+      <c r="I58" s="26">
+        <f t="shared" si="22"/>
+        <v>1.375</v>
+      </c>
+      <c r="J58" s="26">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K58" s="26">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L58" s="17"/>
+      <c r="M58" s="17">
+        <v>26.57</v>
+      </c>
+      <c r="N58" s="17">
+        <v>10</v>
+      </c>
+      <c r="O58" s="34">
+        <f t="shared" si="21"/>
+        <v>36.57</v>
+      </c>
+      <c r="Q58" s="35">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="R58" s="35">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="T58" s="7">
+        <v>16</v>
+      </c>
+      <c r="U58" s="38">
+        <f t="shared" si="23"/>
+        <v>48</v>
+      </c>
+      <c r="V58" s="37"/>
+      <c r="W58" s="37"/>
+      <c r="X58" s="38">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="Y58" s="37"/>
+      <c r="Z58" s="37"/>
+      <c r="AD58" s="7" t="s">
+        <v>258</v>
+      </c>
+      <c r="AE58" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="AF58" s="7">
+        <v>30</v>
+      </c>
+      <c r="AG58" s="7">
+        <v>40</v>
+      </c>
+      <c r="AH58" s="7">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="59" ht="25" customHeight="1" spans="1:34">
+      <c r="A59" s="24" t="s">
+        <v>260</v>
+      </c>
+      <c r="B59" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="C59" s="9">
+        <v>0</v>
+      </c>
+      <c r="D59" s="9">
+        <v>0</v>
+      </c>
+      <c r="E59" s="27">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F59" s="28">
+        <v>1</v>
+      </c>
+      <c r="G59" s="29">
+        <v>1</v>
+      </c>
+      <c r="H59" s="26">
+        <v>1</v>
+      </c>
+      <c r="I59" s="26">
+        <f t="shared" si="22"/>
+        <v>1.375</v>
+      </c>
+      <c r="J59" s="26">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K59" s="26">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L59" s="17"/>
+      <c r="M59" s="17" t="s">
+        <v>164</v>
+      </c>
+      <c r="N59" s="17" t="s">
+        <v>165</v>
+      </c>
+      <c r="O59" s="34">
+        <f t="shared" si="21"/>
+        <v>19</v>
+      </c>
+      <c r="Q59" s="35">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="R59" s="35">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="T59" s="7">
+        <v>32</v>
+      </c>
+      <c r="U59" s="38">
+        <f t="shared" si="23"/>
+        <v>64</v>
+      </c>
+      <c r="V59" s="37"/>
+      <c r="W59" s="37"/>
+      <c r="X59" s="38">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="Y59" s="37"/>
+      <c r="Z59" s="37"/>
+      <c r="AD59" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="AE59" s="7" t="s">
+        <v>263</v>
+      </c>
+      <c r="AF59" s="7">
+        <v>30</v>
+      </c>
+      <c r="AG59" s="7">
+        <v>40</v>
+      </c>
+      <c r="AH59" s="7">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="60" ht="25" customHeight="1" spans="1:34">
+      <c r="A60" s="24" t="s">
+        <v>264</v>
+      </c>
+      <c r="B60" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="C60" s="9">
+        <v>0</v>
+      </c>
+      <c r="D60" s="9">
+        <v>0</v>
+      </c>
+      <c r="E60" s="27">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F60" s="28">
+        <v>1</v>
+      </c>
+      <c r="G60" s="29">
+        <v>1</v>
+      </c>
+      <c r="H60" s="26">
+        <v>1</v>
+      </c>
+      <c r="I60" s="26">
+        <f t="shared" si="22"/>
+        <v>1.375</v>
+      </c>
+      <c r="J60" s="26">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K60" s="26">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="L60" s="17"/>
+      <c r="M60" s="17">
+        <v>26.57</v>
+      </c>
+      <c r="N60" s="17">
+        <v>10</v>
+      </c>
+      <c r="O60" s="34">
+        <f t="shared" si="21"/>
+        <v>36.57</v>
+      </c>
+      <c r="Q60" s="35">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="R60" s="35">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="T60" s="7">
+        <v>16</v>
+      </c>
+      <c r="U60" s="38">
+        <f t="shared" si="23"/>
+        <v>48</v>
+      </c>
+      <c r="V60" s="37"/>
+      <c r="W60" s="37"/>
+      <c r="X60" s="38">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="Y60" s="37"/>
+      <c r="Z60" s="37"/>
+      <c r="AD60" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="AE60" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="AF60" s="7">
+        <v>30</v>
+      </c>
+      <c r="AG60" s="7">
+        <v>40</v>
+      </c>
+      <c r="AH60" s="7">
+        <v>45</v>
+      </c>
+    </row>
     <row r="61" ht="25" customHeight="1"/>
     <row r="62" ht="25" customHeight="1"/>
     <row r="63" ht="25" customHeight="1"/>
@@ -6762,32 +7359,208 @@
     <row r="70" ht="25" customHeight="1"/>
     <row r="71" ht="25" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="A1:AH51">
+  <autoFilter ref="A1:AH54">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="J45">
-    <cfRule type="cellIs" dxfId="0" priority="60" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="0" priority="96" operator="lessThanOrEqual">
+      <formula>70</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="95" operator="lessThanOrEqual">
+      <formula>60</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="94" operator="greaterThanOrEqual">
+      <formula>105</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K45">
+    <cfRule type="cellIs" dxfId="0" priority="93" operator="lessThanOrEqual">
+      <formula>70</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="92" operator="lessThanOrEqual">
+      <formula>60</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="91" operator="greaterThanOrEqual">
+      <formula>105</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J46">
+    <cfRule type="cellIs" dxfId="0" priority="90" operator="lessThanOrEqual">
+      <formula>70</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="89" operator="lessThanOrEqual">
+      <formula>60</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="88" operator="greaterThanOrEqual">
+      <formula>105</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K46">
+    <cfRule type="cellIs" dxfId="0" priority="87" operator="lessThanOrEqual">
+      <formula>70</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="86" operator="lessThanOrEqual">
+      <formula>60</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="85" operator="greaterThanOrEqual">
+      <formula>105</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J47">
+    <cfRule type="cellIs" dxfId="0" priority="84" operator="lessThanOrEqual">
+      <formula>70</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="83" operator="lessThanOrEqual">
+      <formula>60</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="82" operator="greaterThanOrEqual">
+      <formula>105</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K47">
+    <cfRule type="cellIs" dxfId="0" priority="81" operator="lessThanOrEqual">
+      <formula>70</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="80" operator="lessThanOrEqual">
+      <formula>60</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="79" operator="greaterThanOrEqual">
+      <formula>105</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J48">
+    <cfRule type="cellIs" dxfId="0" priority="78" operator="lessThanOrEqual">
+      <formula>70</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="74" operator="lessThanOrEqual">
+      <formula>60</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="70" operator="greaterThanOrEqual">
+      <formula>105</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K48">
+    <cfRule type="cellIs" dxfId="0" priority="66" operator="lessThanOrEqual">
+      <formula>70</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="62" operator="lessThanOrEqual">
+      <formula>60</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="58" operator="greaterThanOrEqual">
+      <formula>105</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J49">
+    <cfRule type="cellIs" dxfId="0" priority="77" operator="lessThanOrEqual">
+      <formula>70</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="73" operator="lessThanOrEqual">
+      <formula>60</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="69" operator="greaterThanOrEqual">
+      <formula>105</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K49">
+    <cfRule type="cellIs" dxfId="0" priority="65" operator="lessThanOrEqual">
+      <formula>70</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="61" operator="lessThanOrEqual">
+      <formula>60</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="57" operator="greaterThanOrEqual">
+      <formula>105</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J50">
+    <cfRule type="cellIs" dxfId="0" priority="76" operator="lessThanOrEqual">
+      <formula>70</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="72" operator="lessThanOrEqual">
+      <formula>60</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="68" operator="greaterThanOrEqual">
+      <formula>105</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K50">
+    <cfRule type="cellIs" dxfId="0" priority="64" operator="lessThanOrEqual">
+      <formula>70</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="60" operator="lessThanOrEqual">
+      <formula>60</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="56" operator="greaterThanOrEqual">
+      <formula>105</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J51">
+    <cfRule type="cellIs" dxfId="0" priority="75" operator="lessThanOrEqual">
+      <formula>70</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="71" operator="lessThanOrEqual">
+      <formula>60</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="67" operator="greaterThanOrEqual">
+      <formula>105</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K51">
+    <cfRule type="cellIs" dxfId="0" priority="63" operator="lessThanOrEqual">
       <formula>70</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="1" priority="59" operator="lessThanOrEqual">
       <formula>60</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="58" operator="greaterThanOrEqual">
-      <formula>105</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K45">
-    <cfRule type="cellIs" dxfId="0" priority="57" operator="lessThanOrEqual">
-      <formula>70</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="56" operator="lessThanOrEqual">
-      <formula>60</formula>
-    </cfRule>
     <cfRule type="cellIs" dxfId="2" priority="55" operator="greaterThanOrEqual">
       <formula>105</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J46">
+  <conditionalFormatting sqref="J52">
+    <cfRule type="cellIs" dxfId="0" priority="48" operator="lessThanOrEqual">
+      <formula>70</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="47" operator="lessThanOrEqual">
+      <formula>60</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="46" operator="greaterThanOrEqual">
+      <formula>105</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K52">
+    <cfRule type="cellIs" dxfId="0" priority="45" operator="lessThanOrEqual">
+      <formula>70</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="44" operator="lessThanOrEqual">
+      <formula>60</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="43" operator="greaterThanOrEqual">
+      <formula>105</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J53">
+    <cfRule type="cellIs" dxfId="0" priority="42" operator="lessThanOrEqual">
+      <formula>70</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="41" operator="lessThanOrEqual">
+      <formula>60</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="40" operator="greaterThanOrEqual">
+      <formula>105</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K53">
+    <cfRule type="cellIs" dxfId="0" priority="39" operator="lessThanOrEqual">
+      <formula>70</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="38" operator="lessThanOrEqual">
+      <formula>60</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="37" operator="greaterThanOrEqual">
+      <formula>105</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J54">
     <cfRule type="cellIs" dxfId="0" priority="54" operator="lessThanOrEqual">
       <formula>70</formula>
     </cfRule>
@@ -6798,7 +7571,7 @@
       <formula>105</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K46">
+  <conditionalFormatting sqref="K54">
     <cfRule type="cellIs" dxfId="0" priority="51" operator="lessThanOrEqual">
       <formula>70</formula>
     </cfRule>
@@ -6809,117 +7582,95 @@
       <formula>105</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J47">
-    <cfRule type="cellIs" dxfId="0" priority="48" operator="lessThanOrEqual">
+  <conditionalFormatting sqref="J55">
+    <cfRule type="cellIs" dxfId="0" priority="36" operator="lessThanOrEqual">
       <formula>70</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="47" operator="lessThanOrEqual">
-      <formula>60</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="46" operator="greaterThanOrEqual">
-      <formula>105</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K47">
-    <cfRule type="cellIs" dxfId="0" priority="45" operator="lessThanOrEqual">
-      <formula>70</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="44" operator="lessThanOrEqual">
-      <formula>60</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="43" operator="greaterThanOrEqual">
-      <formula>105</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J48">
-    <cfRule type="cellIs" dxfId="0" priority="42" operator="lessThanOrEqual">
-      <formula>70</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="38" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="1" priority="35" operator="lessThanOrEqual">
       <formula>60</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="2" priority="34" operator="greaterThanOrEqual">
       <formula>105</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K48">
+  <conditionalFormatting sqref="K55">
+    <cfRule type="cellIs" dxfId="0" priority="33" operator="lessThanOrEqual">
+      <formula>70</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="32" operator="lessThanOrEqual">
+      <formula>60</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="31" operator="greaterThanOrEqual">
+      <formula>105</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J56">
     <cfRule type="cellIs" dxfId="0" priority="30" operator="lessThanOrEqual">
       <formula>70</formula>
     </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="29" operator="lessThanOrEqual">
+      <formula>60</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="28" operator="greaterThanOrEqual">
+      <formula>105</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K56">
+    <cfRule type="cellIs" dxfId="0" priority="27" operator="lessThanOrEqual">
+      <formula>70</formula>
+    </cfRule>
     <cfRule type="cellIs" dxfId="1" priority="26" operator="lessThanOrEqual">
       <formula>60</formula>
     </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="25" operator="greaterThanOrEqual">
+      <formula>105</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J57">
+    <cfRule type="cellIs" dxfId="0" priority="24" operator="lessThanOrEqual">
+      <formula>70</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="23" operator="lessThanOrEqual">
+      <formula>60</formula>
+    </cfRule>
     <cfRule type="cellIs" dxfId="2" priority="22" operator="greaterThanOrEqual">
       <formula>105</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J49">
-    <cfRule type="cellIs" dxfId="0" priority="41" operator="lessThanOrEqual">
+  <conditionalFormatting sqref="K57">
+    <cfRule type="cellIs" dxfId="0" priority="21" operator="lessThanOrEqual">
       <formula>70</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="37" operator="lessThanOrEqual">
-      <formula>60</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="33" operator="greaterThanOrEqual">
-      <formula>105</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K49">
-    <cfRule type="cellIs" dxfId="0" priority="29" operator="lessThanOrEqual">
-      <formula>70</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="25" operator="lessThanOrEqual">
-      <formula>60</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="21" operator="greaterThanOrEqual">
-      <formula>105</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J50">
-    <cfRule type="cellIs" dxfId="0" priority="40" operator="lessThanOrEqual">
-      <formula>70</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="36" operator="lessThanOrEqual">
-      <formula>60</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="32" operator="greaterThanOrEqual">
-      <formula>105</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K50">
-    <cfRule type="cellIs" dxfId="0" priority="28" operator="lessThanOrEqual">
-      <formula>70</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="24" operator="lessThanOrEqual">
-      <formula>60</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="20" operator="greaterThanOrEqual">
-      <formula>105</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J51">
-    <cfRule type="cellIs" dxfId="0" priority="39" operator="lessThanOrEqual">
-      <formula>70</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="35" operator="lessThanOrEqual">
-      <formula>60</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="31" operator="greaterThanOrEqual">
-      <formula>105</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K51">
-    <cfRule type="cellIs" dxfId="0" priority="27" operator="lessThanOrEqual">
-      <formula>70</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="23" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="1" priority="20" operator="lessThanOrEqual">
       <formula>60</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="2" priority="19" operator="greaterThanOrEqual">
       <formula>105</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J52">
+  <conditionalFormatting sqref="J58">
+    <cfRule type="cellIs" dxfId="0" priority="18" operator="lessThanOrEqual">
+      <formula>70</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="17" operator="lessThanOrEqual">
+      <formula>60</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="16" operator="greaterThanOrEqual">
+      <formula>105</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K58">
+    <cfRule type="cellIs" dxfId="0" priority="15" operator="lessThanOrEqual">
+      <formula>70</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="14" operator="lessThanOrEqual">
+      <formula>60</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="13" operator="greaterThanOrEqual">
+      <formula>105</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J59">
     <cfRule type="cellIs" dxfId="0" priority="12" operator="lessThanOrEqual">
       <formula>70</formula>
     </cfRule>
@@ -6930,7 +7681,7 @@
       <formula>105</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K52">
+  <conditionalFormatting sqref="K59">
     <cfRule type="cellIs" dxfId="0" priority="9" operator="lessThanOrEqual">
       <formula>70</formula>
     </cfRule>
@@ -6941,7 +7692,7 @@
       <formula>105</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J53">
+  <conditionalFormatting sqref="J60">
     <cfRule type="cellIs" dxfId="0" priority="6" operator="lessThanOrEqual">
       <formula>70</formula>
     </cfRule>
@@ -6952,7 +7703,7 @@
       <formula>105</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K53">
+  <conditionalFormatting sqref="K60">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThanOrEqual">
       <formula>70</formula>
     </cfRule>
@@ -6963,69 +7714,47 @@
       <formula>105</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J54">
-    <cfRule type="cellIs" dxfId="0" priority="18" operator="lessThanOrEqual">
-      <formula>70</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="17" operator="lessThanOrEqual">
+  <conditionalFormatting sqref="J2:J29">
+    <cfRule type="cellIs" dxfId="2" priority="109" operator="greaterThanOrEqual">
+      <formula>105</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="110" operator="lessThanOrEqual">
       <formula>60</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="16" operator="greaterThanOrEqual">
-      <formula>105</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K54">
-    <cfRule type="cellIs" dxfId="0" priority="15" operator="lessThanOrEqual">
-      <formula>70</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="14" operator="lessThanOrEqual">
-      <formula>60</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="13" operator="greaterThanOrEqual">
-      <formula>105</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J29">
-    <cfRule type="cellIs" dxfId="2" priority="73" operator="greaterThanOrEqual">
-      <formula>105</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="74" operator="lessThanOrEqual">
-      <formula>60</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="75" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="0" priority="111" operator="lessThanOrEqual">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J30:J44">
-    <cfRule type="cellIs" dxfId="2" priority="67" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="2" priority="103" operator="greaterThanOrEqual">
       <formula>105</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="68" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="1" priority="104" operator="lessThanOrEqual">
       <formula>60</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="69" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="0" priority="105" operator="lessThanOrEqual">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K29">
-    <cfRule type="cellIs" dxfId="2" priority="64" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="2" priority="100" operator="greaterThanOrEqual">
       <formula>105</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="65" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="1" priority="101" operator="lessThanOrEqual">
       <formula>60</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="66" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="0" priority="102" operator="lessThanOrEqual">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="K30:K44">
-    <cfRule type="cellIs" dxfId="2" priority="61" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="2" priority="97" operator="greaterThanOrEqual">
       <formula>105</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="62" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="1" priority="98" operator="lessThanOrEqual">
       <formula>60</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="63" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="0" priority="99" operator="lessThanOrEqual">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>

--- a/dist/产品库存及周转统计.xlsx
+++ b/dist/产品库存及周转统计.xlsx
@@ -4,20 +4,20 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16160"/>
+    <workbookView windowHeight="15240"/>
   </bookViews>
   <sheets>
     <sheet name="产品库存" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">产品库存!$A$1:$AH$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">产品库存!$A$1:$AH$60</definedName>
   </definedNames>
   <calcPr calcId="144525" concurrentCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="268">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="286" uniqueCount="276">
   <si>
     <t>名称</t>
   </si>
@@ -835,6 +835,30 @@
   </si>
   <si>
     <t>X005166XCN</t>
+  </si>
+  <si>
+    <t>【小】灰色B款(2p)</t>
+  </si>
+  <si>
+    <t>B0GWWS56G5</t>
+  </si>
+  <si>
+    <t>WallHangingBagSmallGray_2P_B</t>
+  </si>
+  <si>
+    <t>X0052N791J</t>
+  </si>
+  <si>
+    <t>【小】白色B款(2p)</t>
+  </si>
+  <si>
+    <t>B0GWWP5MT7</t>
+  </si>
+  <si>
+    <t>WallHangingBagSmallWhite_2P_B</t>
+  </si>
+  <si>
+    <t>X0052N76DZ</t>
   </si>
 </sst>
 </file>
@@ -2165,7 +2189,7 @@
         <v>0</v>
       </c>
       <c r="E2" s="27">
-        <f t="shared" ref="E2:E60" si="0">C2+D2</f>
+        <f t="shared" ref="E2:E62" si="0">C2+D2</f>
         <v>0</v>
       </c>
       <c r="F2" s="28">
@@ -2182,11 +2206,11 @@
         <v>22.55</v>
       </c>
       <c r="J2" s="26">
-        <f t="shared" ref="J2:J60" si="2">(C2)/I2</f>
+        <f t="shared" ref="J2:J62" si="2">(C2)/I2</f>
         <v>0</v>
       </c>
       <c r="K2" s="26">
-        <f t="shared" ref="K2:K60" si="3">(E2)/I2</f>
+        <f t="shared" ref="K2:K62" si="3">(E2)/I2</f>
         <v>0</v>
       </c>
       <c r="L2" s="17"/>
@@ -5996,11 +6020,11 @@
         <v>51</v>
       </c>
       <c r="Q45" s="35">
-        <f t="shared" ref="Q45:Q60" si="17">M45*C45</f>
+        <f t="shared" ref="Q45:Q62" si="17">M45*C45</f>
         <v>0</v>
       </c>
       <c r="R45" s="35">
-        <f t="shared" ref="R45:R60" si="18">M45*D45</f>
+        <f t="shared" ref="R45:R62" si="18">M45*D45</f>
         <v>0</v>
       </c>
       <c r="T45" s="7">
@@ -6079,7 +6103,7 @@
         <v>6</v>
       </c>
       <c r="O46" s="34">
-        <f t="shared" ref="O46:O60" si="21">M46+N46</f>
+        <f t="shared" ref="O46:O62" si="21">M46+N46</f>
         <v>25.5</v>
       </c>
       <c r="Q46" s="35">
@@ -7056,13 +7080,13 @@
         <v>32</v>
       </c>
       <c r="U57" s="38">
-        <f t="shared" ref="U57:U60" si="23">CEILING(MAX(0,90-MAX(K57,60))*I57/T57,1)*T57</f>
+        <f t="shared" ref="U57:U62" si="23">CEILING(MAX(0,90-MAX(K57,60))*I57/T57,1)*T57</f>
         <v>64</v>
       </c>
       <c r="V57" s="37"/>
       <c r="W57" s="37"/>
       <c r="X57" s="38">
-        <f t="shared" ref="X57:X60" si="24">MIN(CEILING(MAX(0,70-MAX(J57,30))*I57/T57,1)*T57,D57)</f>
+        <f t="shared" ref="X57:X62" si="24">MIN(CEILING(MAX(0,70-MAX(J57,30))*I57/T57,1)*T57,D57)</f>
         <v>0</v>
       </c>
       <c r="Y57" s="37"/>
@@ -7347,8 +7371,180 @@
         <v>45</v>
       </c>
     </row>
-    <row r="61" ht="25" customHeight="1"/>
-    <row r="62" ht="25" customHeight="1"/>
+    <row r="61" ht="25" customHeight="1" spans="1:34">
+      <c r="A61" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="C61" s="9">
+        <v>0</v>
+      </c>
+      <c r="D61" s="9">
+        <v>0</v>
+      </c>
+      <c r="E61" s="27">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F61" s="7">
+        <v>0</v>
+      </c>
+      <c r="G61" s="7">
+        <v>0</v>
+      </c>
+      <c r="H61" s="26">
+        <f>MAX(E61,F61)*1.375</f>
+        <v>0</v>
+      </c>
+      <c r="I61" s="26">
+        <v>1</v>
+      </c>
+      <c r="J61" s="26">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K61" s="26">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M61" s="7">
+        <v>18</v>
+      </c>
+      <c r="N61" s="17">
+        <v>6</v>
+      </c>
+      <c r="O61" s="34">
+        <f t="shared" si="21"/>
+        <v>24</v>
+      </c>
+      <c r="Q61" s="35">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="R61" s="35">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="T61" s="7">
+        <v>20</v>
+      </c>
+      <c r="U61" s="38">
+        <f t="shared" si="23"/>
+        <v>40</v>
+      </c>
+      <c r="V61" s="37"/>
+      <c r="W61" s="37"/>
+      <c r="X61" s="38">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="Y61" s="37"/>
+      <c r="Z61" s="37"/>
+      <c r="AD61" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="AE61" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="AF61" s="7">
+        <v>25</v>
+      </c>
+      <c r="AG61" s="7">
+        <v>37</v>
+      </c>
+      <c r="AH61" s="7">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="62" ht="25" customHeight="1" spans="1:34">
+      <c r="A62" s="7" t="s">
+        <v>272</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>273</v>
+      </c>
+      <c r="C62" s="9">
+        <v>0</v>
+      </c>
+      <c r="D62" s="9">
+        <v>0</v>
+      </c>
+      <c r="E62" s="27">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="F62" s="7">
+        <v>0</v>
+      </c>
+      <c r="G62" s="7">
+        <v>0</v>
+      </c>
+      <c r="H62" s="26">
+        <f>MAX(E62,F62)*1.375</f>
+        <v>0</v>
+      </c>
+      <c r="I62" s="26">
+        <v>1</v>
+      </c>
+      <c r="J62" s="26">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="K62" s="26">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="M62" s="7">
+        <v>18</v>
+      </c>
+      <c r="N62" s="17">
+        <v>6</v>
+      </c>
+      <c r="O62" s="34">
+        <f t="shared" si="21"/>
+        <v>24</v>
+      </c>
+      <c r="Q62" s="35">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
+      <c r="R62" s="35">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="T62" s="7">
+        <v>20</v>
+      </c>
+      <c r="U62" s="38">
+        <f t="shared" si="23"/>
+        <v>40</v>
+      </c>
+      <c r="V62" s="37"/>
+      <c r="W62" s="37"/>
+      <c r="X62" s="38">
+        <f t="shared" si="24"/>
+        <v>0</v>
+      </c>
+      <c r="Y62" s="37"/>
+      <c r="Z62" s="37"/>
+      <c r="AD62" s="7" t="s">
+        <v>274</v>
+      </c>
+      <c r="AE62" s="7" t="s">
+        <v>275</v>
+      </c>
+      <c r="AF62" s="7">
+        <v>25</v>
+      </c>
+      <c r="AG62" s="7">
+        <v>37</v>
+      </c>
+      <c r="AH62" s="7">
+        <v>40</v>
+      </c>
+    </row>
     <row r="63" ht="25" customHeight="1"/>
     <row r="64" ht="25" customHeight="1"/>
     <row r="65" ht="25" customHeight="1"/>
@@ -7359,10 +7555,54 @@
     <row r="70" ht="25" customHeight="1"/>
     <row r="71" ht="25" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="A1:AH54">
+  <autoFilter ref="A1:AH60">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="J45">
+    <cfRule type="cellIs" dxfId="0" priority="108" operator="lessThanOrEqual">
+      <formula>70</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="107" operator="lessThanOrEqual">
+      <formula>60</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="106" operator="greaterThanOrEqual">
+      <formula>105</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K45">
+    <cfRule type="cellIs" dxfId="0" priority="105" operator="lessThanOrEqual">
+      <formula>70</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="104" operator="lessThanOrEqual">
+      <formula>60</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="103" operator="greaterThanOrEqual">
+      <formula>105</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J46">
+    <cfRule type="cellIs" dxfId="0" priority="102" operator="lessThanOrEqual">
+      <formula>70</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="101" operator="lessThanOrEqual">
+      <formula>60</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="100" operator="greaterThanOrEqual">
+      <formula>105</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K46">
+    <cfRule type="cellIs" dxfId="0" priority="99" operator="lessThanOrEqual">
+      <formula>70</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="98" operator="lessThanOrEqual">
+      <formula>60</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="97" operator="greaterThanOrEqual">
+      <formula>105</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J47">
     <cfRule type="cellIs" dxfId="0" priority="96" operator="lessThanOrEqual">
       <formula>70</formula>
     </cfRule>
@@ -7373,7 +7613,7 @@
       <formula>105</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K45">
+  <conditionalFormatting sqref="K47">
     <cfRule type="cellIs" dxfId="0" priority="93" operator="lessThanOrEqual">
       <formula>70</formula>
     </cfRule>
@@ -7384,139 +7624,161 @@
       <formula>105</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J46">
+  <conditionalFormatting sqref="J48">
     <cfRule type="cellIs" dxfId="0" priority="90" operator="lessThanOrEqual">
       <formula>70</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="89" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="1" priority="86" operator="lessThanOrEqual">
       <formula>60</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="88" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="2" priority="82" operator="greaterThanOrEqual">
       <formula>105</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K46">
+  <conditionalFormatting sqref="K48">
+    <cfRule type="cellIs" dxfId="0" priority="78" operator="lessThanOrEqual">
+      <formula>70</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="74" operator="lessThanOrEqual">
+      <formula>60</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="70" operator="greaterThanOrEqual">
+      <formula>105</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J49">
+    <cfRule type="cellIs" dxfId="0" priority="89" operator="lessThanOrEqual">
+      <formula>70</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="85" operator="lessThanOrEqual">
+      <formula>60</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="81" operator="greaterThanOrEqual">
+      <formula>105</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K49">
+    <cfRule type="cellIs" dxfId="0" priority="77" operator="lessThanOrEqual">
+      <formula>70</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="73" operator="lessThanOrEqual">
+      <formula>60</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="69" operator="greaterThanOrEqual">
+      <formula>105</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J50">
+    <cfRule type="cellIs" dxfId="0" priority="88" operator="lessThanOrEqual">
+      <formula>70</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="84" operator="lessThanOrEqual">
+      <formula>60</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="80" operator="greaterThanOrEqual">
+      <formula>105</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K50">
+    <cfRule type="cellIs" dxfId="0" priority="76" operator="lessThanOrEqual">
+      <formula>70</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="72" operator="lessThanOrEqual">
+      <formula>60</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="68" operator="greaterThanOrEqual">
+      <formula>105</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J51">
     <cfRule type="cellIs" dxfId="0" priority="87" operator="lessThanOrEqual">
       <formula>70</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="86" operator="lessThanOrEqual">
-      <formula>60</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="85" operator="greaterThanOrEqual">
-      <formula>105</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J47">
-    <cfRule type="cellIs" dxfId="0" priority="84" operator="lessThanOrEqual">
-      <formula>70</formula>
-    </cfRule>
     <cfRule type="cellIs" dxfId="1" priority="83" operator="lessThanOrEqual">
       <formula>60</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="82" operator="greaterThanOrEqual">
-      <formula>105</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K47">
-    <cfRule type="cellIs" dxfId="0" priority="81" operator="lessThanOrEqual">
-      <formula>70</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="80" operator="lessThanOrEqual">
-      <formula>60</formula>
-    </cfRule>
     <cfRule type="cellIs" dxfId="2" priority="79" operator="greaterThanOrEqual">
       <formula>105</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J48">
-    <cfRule type="cellIs" dxfId="0" priority="78" operator="lessThanOrEqual">
+  <conditionalFormatting sqref="K51">
+    <cfRule type="cellIs" dxfId="0" priority="75" operator="lessThanOrEqual">
       <formula>70</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="74" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="1" priority="71" operator="lessThanOrEqual">
       <formula>60</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="70" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="2" priority="67" operator="greaterThanOrEqual">
       <formula>105</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K48">
+  <conditionalFormatting sqref="J52">
+    <cfRule type="cellIs" dxfId="0" priority="60" operator="lessThanOrEqual">
+      <formula>70</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="59" operator="lessThanOrEqual">
+      <formula>60</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="58" operator="greaterThanOrEqual">
+      <formula>105</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K52">
+    <cfRule type="cellIs" dxfId="0" priority="57" operator="lessThanOrEqual">
+      <formula>70</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="56" operator="lessThanOrEqual">
+      <formula>60</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="55" operator="greaterThanOrEqual">
+      <formula>105</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J53">
+    <cfRule type="cellIs" dxfId="0" priority="54" operator="lessThanOrEqual">
+      <formula>70</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="53" operator="lessThanOrEqual">
+      <formula>60</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="52" operator="greaterThanOrEqual">
+      <formula>105</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K53">
+    <cfRule type="cellIs" dxfId="0" priority="51" operator="lessThanOrEqual">
+      <formula>70</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="50" operator="lessThanOrEqual">
+      <formula>60</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="49" operator="greaterThanOrEqual">
+      <formula>105</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J54">
     <cfRule type="cellIs" dxfId="0" priority="66" operator="lessThanOrEqual">
       <formula>70</formula>
     </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="65" operator="lessThanOrEqual">
+      <formula>60</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="64" operator="greaterThanOrEqual">
+      <formula>105</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K54">
+    <cfRule type="cellIs" dxfId="0" priority="63" operator="lessThanOrEqual">
+      <formula>70</formula>
+    </cfRule>
     <cfRule type="cellIs" dxfId="1" priority="62" operator="lessThanOrEqual">
       <formula>60</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="58" operator="greaterThanOrEqual">
+    <cfRule type="cellIs" dxfId="2" priority="61" operator="greaterThanOrEqual">
       <formula>105</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J49">
-    <cfRule type="cellIs" dxfId="0" priority="77" operator="lessThanOrEqual">
-      <formula>70</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="73" operator="lessThanOrEqual">
-      <formula>60</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="69" operator="greaterThanOrEqual">
-      <formula>105</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K49">
-    <cfRule type="cellIs" dxfId="0" priority="65" operator="lessThanOrEqual">
-      <formula>70</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="61" operator="lessThanOrEqual">
-      <formula>60</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="57" operator="greaterThanOrEqual">
-      <formula>105</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J50">
-    <cfRule type="cellIs" dxfId="0" priority="76" operator="lessThanOrEqual">
-      <formula>70</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="72" operator="lessThanOrEqual">
-      <formula>60</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="68" operator="greaterThanOrEqual">
-      <formula>105</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K50">
-    <cfRule type="cellIs" dxfId="0" priority="64" operator="lessThanOrEqual">
-      <formula>70</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="60" operator="lessThanOrEqual">
-      <formula>60</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="56" operator="greaterThanOrEqual">
-      <formula>105</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J51">
-    <cfRule type="cellIs" dxfId="0" priority="75" operator="lessThanOrEqual">
-      <formula>70</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="71" operator="lessThanOrEqual">
-      <formula>60</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="67" operator="greaterThanOrEqual">
-      <formula>105</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K51">
-    <cfRule type="cellIs" dxfId="0" priority="63" operator="lessThanOrEqual">
-      <formula>70</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="59" operator="lessThanOrEqual">
-      <formula>60</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="55" operator="greaterThanOrEqual">
-      <formula>105</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J52">
+  <conditionalFormatting sqref="J55">
     <cfRule type="cellIs" dxfId="0" priority="48" operator="lessThanOrEqual">
       <formula>70</formula>
     </cfRule>
@@ -7527,7 +7789,7 @@
       <formula>105</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K52">
+  <conditionalFormatting sqref="K55">
     <cfRule type="cellIs" dxfId="0" priority="45" operator="lessThanOrEqual">
       <formula>70</formula>
     </cfRule>
@@ -7538,7 +7800,7 @@
       <formula>105</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J53">
+  <conditionalFormatting sqref="J56">
     <cfRule type="cellIs" dxfId="0" priority="42" operator="lessThanOrEqual">
       <formula>70</formula>
     </cfRule>
@@ -7549,7 +7811,7 @@
       <formula>105</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K53">
+  <conditionalFormatting sqref="K56">
     <cfRule type="cellIs" dxfId="0" priority="39" operator="lessThanOrEqual">
       <formula>70</formula>
     </cfRule>
@@ -7560,29 +7822,7 @@
       <formula>105</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J54">
-    <cfRule type="cellIs" dxfId="0" priority="54" operator="lessThanOrEqual">
-      <formula>70</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="53" operator="lessThanOrEqual">
-      <formula>60</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="52" operator="greaterThanOrEqual">
-      <formula>105</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K54">
-    <cfRule type="cellIs" dxfId="0" priority="51" operator="lessThanOrEqual">
-      <formula>70</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="50" operator="lessThanOrEqual">
-      <formula>60</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="49" operator="greaterThanOrEqual">
-      <formula>105</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J55">
+  <conditionalFormatting sqref="J57">
     <cfRule type="cellIs" dxfId="0" priority="36" operator="lessThanOrEqual">
       <formula>70</formula>
     </cfRule>
@@ -7593,7 +7833,7 @@
       <formula>105</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K55">
+  <conditionalFormatting sqref="K57">
     <cfRule type="cellIs" dxfId="0" priority="33" operator="lessThanOrEqual">
       <formula>70</formula>
     </cfRule>
@@ -7604,7 +7844,7 @@
       <formula>105</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J56">
+  <conditionalFormatting sqref="J58">
     <cfRule type="cellIs" dxfId="0" priority="30" operator="lessThanOrEqual">
       <formula>70</formula>
     </cfRule>
@@ -7615,7 +7855,7 @@
       <formula>105</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K56">
+  <conditionalFormatting sqref="K58">
     <cfRule type="cellIs" dxfId="0" priority="27" operator="lessThanOrEqual">
       <formula>70</formula>
     </cfRule>
@@ -7626,7 +7866,7 @@
       <formula>105</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J57">
+  <conditionalFormatting sqref="J59">
     <cfRule type="cellIs" dxfId="0" priority="24" operator="lessThanOrEqual">
       <formula>70</formula>
     </cfRule>
@@ -7637,7 +7877,7 @@
       <formula>105</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K57">
+  <conditionalFormatting sqref="K59">
     <cfRule type="cellIs" dxfId="0" priority="21" operator="lessThanOrEqual">
       <formula>70</formula>
     </cfRule>
@@ -7648,7 +7888,7 @@
       <formula>105</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J58">
+  <conditionalFormatting sqref="J60">
     <cfRule type="cellIs" dxfId="0" priority="18" operator="lessThanOrEqual">
       <formula>70</formula>
     </cfRule>
@@ -7659,7 +7899,7 @@
       <formula>105</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K58">
+  <conditionalFormatting sqref="K60">
     <cfRule type="cellIs" dxfId="0" priority="15" operator="lessThanOrEqual">
       <formula>70</formula>
     </cfRule>
@@ -7670,7 +7910,7 @@
       <formula>105</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J59">
+  <conditionalFormatting sqref="J61">
     <cfRule type="cellIs" dxfId="0" priority="12" operator="lessThanOrEqual">
       <formula>70</formula>
     </cfRule>
@@ -7681,7 +7921,7 @@
       <formula>105</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K59">
+  <conditionalFormatting sqref="K61">
     <cfRule type="cellIs" dxfId="0" priority="9" operator="lessThanOrEqual">
       <formula>70</formula>
     </cfRule>
@@ -7692,7 +7932,7 @@
       <formula>105</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J60">
+  <conditionalFormatting sqref="J62">
     <cfRule type="cellIs" dxfId="0" priority="6" operator="lessThanOrEqual">
       <formula>70</formula>
     </cfRule>
@@ -7703,7 +7943,7 @@
       <formula>105</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K60">
+  <conditionalFormatting sqref="K62">
     <cfRule type="cellIs" dxfId="0" priority="3" operator="lessThanOrEqual">
       <formula>70</formula>
     </cfRule>
@@ -7715,6 +7955,39 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="J2:J29">
+    <cfRule type="cellIs" dxfId="2" priority="121" operator="greaterThanOrEqual">
+      <formula>105</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="122" operator="lessThanOrEqual">
+      <formula>60</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="123" operator="lessThanOrEqual">
+      <formula>70</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J30:J44">
+    <cfRule type="cellIs" dxfId="2" priority="115" operator="greaterThanOrEqual">
+      <formula>105</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="116" operator="lessThanOrEqual">
+      <formula>60</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="117" operator="lessThanOrEqual">
+      <formula>70</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K2:K29">
+    <cfRule type="cellIs" dxfId="2" priority="112" operator="greaterThanOrEqual">
+      <formula>105</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="113" operator="lessThanOrEqual">
+      <formula>60</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="114" operator="lessThanOrEqual">
+      <formula>70</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K30:K44">
     <cfRule type="cellIs" dxfId="2" priority="109" operator="greaterThanOrEqual">
       <formula>105</formula>
     </cfRule>
@@ -7722,39 +7995,6 @@
       <formula>60</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="0" priority="111" operator="lessThanOrEqual">
-      <formula>70</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J30:J44">
-    <cfRule type="cellIs" dxfId="2" priority="103" operator="greaterThanOrEqual">
-      <formula>105</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="104" operator="lessThanOrEqual">
-      <formula>60</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="105" operator="lessThanOrEqual">
-      <formula>70</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K29">
-    <cfRule type="cellIs" dxfId="2" priority="100" operator="greaterThanOrEqual">
-      <formula>105</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="101" operator="lessThanOrEqual">
-      <formula>60</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="102" operator="lessThanOrEqual">
-      <formula>70</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K30:K44">
-    <cfRule type="cellIs" dxfId="2" priority="97" operator="greaterThanOrEqual">
-      <formula>105</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="98" operator="lessThanOrEqual">
-      <formula>60</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="99" operator="lessThanOrEqual">
       <formula>70</formula>
     </cfRule>
   </conditionalFormatting>

--- a/dist/产品库存及周转统计.xlsx
+++ b/dist/产品库存及周转统计.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="23040"/>
+    <workbookView windowHeight="15240"/>
   </bookViews>
   <sheets>
     <sheet name="产品库存" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">产品库存!$A$1:$AH$62</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">产品库存!$A$1:$AH$60</definedName>
   </definedNames>
   <calcPr calcId="144525" concurrentCalc="0"/>
 </workbook>
@@ -5941,11 +5941,11 @@
         <v>0</v>
       </c>
       <c r="T44" s="7">
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="U44" s="38">
         <f t="shared" si="14"/>
-        <v>40</v>
+        <v>72</v>
       </c>
       <c r="V44" s="37"/>
       <c r="W44" s="37"/>
@@ -5962,7 +5962,7 @@
         <v>205</v>
       </c>
       <c r="AF44" s="7">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="AG44" s="7">
         <v>37</v>
@@ -7555,7 +7555,7 @@
     <row r="70" ht="25" customHeight="1"/>
     <row r="71" ht="25" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="A1:AH62">
+  <autoFilter ref="A1:AH60">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="J45">

--- a/dist/产品库存及周转统计.xlsx
+++ b/dist/产品库存及周转统计.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15240"/>
+    <workbookView windowHeight="23040"/>
   </bookViews>
   <sheets>
     <sheet name="产品库存" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">产品库存!$A$1:$AH$60</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">产品库存!$A$1:$AH$62</definedName>
   </definedNames>
   <calcPr calcId="144525" concurrentCalc="0"/>
 </workbook>
@@ -5941,11 +5941,11 @@
         <v>0</v>
       </c>
       <c r="T44" s="7">
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="U44" s="38">
         <f t="shared" si="14"/>
-        <v>72</v>
+        <v>40</v>
       </c>
       <c r="V44" s="37"/>
       <c r="W44" s="37"/>
@@ -5962,7 +5962,7 @@
         <v>205</v>
       </c>
       <c r="AF44" s="7">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="AG44" s="7">
         <v>37</v>
@@ -7555,7 +7555,7 @@
     <row r="70" ht="25" customHeight="1"/>
     <row r="71" ht="25" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="A1:AH60">
+  <autoFilter ref="A1:AH62">
     <extLst/>
   </autoFilter>
   <conditionalFormatting sqref="J45">
